--- a/AirAgOps_Chart_of_Accounts.xlsx
+++ b/AirAgOps_Chart_of_Accounts.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O233"/>
+  <dimension ref="A1:O234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10512,189 +10512,183 @@
       <c r="O146" s="10" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="n">
+      <c r="A147" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Miscellaneous and other income</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Postable</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>AirAg Ops only</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Invoicing</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Other Primary Income</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>coa.4800.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="n">
         <v>4900</v>
       </c>
-      <c r="B147" s="10" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>Sales discounts, rebates and allowances</t>
         </is>
       </c>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="C148" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
         <is>
           <t>Postable</t>
         </is>
       </c>
-      <c r="E147" s="9" t="inlineStr">
+      <c r="E148" s="9" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr">
+      <c r="F148" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G147" s="9" t="inlineStr">
+      <c r="G148" s="9" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="H147" s="9" t="inlineStr">
+      <c r="H148" s="9" t="inlineStr">
         <is>
           <t>AirAg Ops only</t>
         </is>
       </c>
-      <c r="I147" s="9" t="inlineStr">
+      <c r="I148" s="9" t="inlineStr">
         <is>
           <t>Invoicing</t>
         </is>
       </c>
-      <c r="J147" s="9" t="inlineStr">
+      <c r="J148" s="9" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="K147" s="10" t="inlineStr">
+      <c r="K148" s="10" t="inlineStr">
         <is>
           <t>Discounts/Refunds Given</t>
         </is>
       </c>
-      <c r="L147" s="9" t="inlineStr">
+      <c r="L148" s="9" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="M147" s="9" t="inlineStr">
+      <c r="M148" s="9" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="N147" s="9" t="inlineStr">
+      <c r="N148" s="9" t="inlineStr">
         <is>
           <t>coa.4900.name</t>
         </is>
       </c>
-      <c r="O147" s="10" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="7" t="n">
+      <c r="O148" s="10" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="n">
         <v>5000</v>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>Direct costs – flight operations</t>
         </is>
       </c>
-      <c r="C148" s="7" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="E148" s="7" t="inlineStr"/>
-      <c r="F148" s="7" t="inlineStr"/>
-      <c r="G148" s="7" t="inlineStr"/>
-      <c r="H148" s="7" t="inlineStr"/>
-      <c r="I148" s="7" t="inlineStr"/>
-      <c r="J148" s="7" t="inlineStr"/>
-      <c r="K148" s="8" t="inlineStr"/>
-      <c r="L148" s="7" t="inlineStr"/>
-      <c r="M148" s="7" t="inlineStr"/>
-      <c r="N148" s="7" t="inlineStr">
+      <c r="E149" s="7" t="inlineStr"/>
+      <c r="F149" s="7" t="inlineStr"/>
+      <c r="G149" s="7" t="inlineStr"/>
+      <c r="H149" s="7" t="inlineStr"/>
+      <c r="I149" s="7" t="inlineStr"/>
+      <c r="J149" s="7" t="inlineStr"/>
+      <c r="K149" s="8" t="inlineStr"/>
+      <c r="L149" s="7" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+      <c r="N149" s="7" t="inlineStr">
         <is>
           <t>coa.5000.name</t>
         </is>
       </c>
-      <c r="O148" s="8" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="n">
-        <v>5010</v>
-      </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>Chemical cost of sales (company-owned)</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>Postable</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr"/>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H149" s="9" t="inlineStr">
-        <is>
-          <t>AirAg Ops only</t>
-        </is>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>Chemical Inventory</t>
-        </is>
-      </c>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="K149" s="10" t="inlineStr">
-        <is>
-          <t>Supplies &amp; Materials - COGS</t>
-        </is>
-      </c>
-      <c r="L149" s="9" t="inlineStr">
-        <is>
-          <t>8320</t>
-        </is>
-      </c>
-      <c r="M149" s="9" t="inlineStr">
-        <is>
-          <t>2 (1125-A)</t>
-        </is>
-      </c>
-      <c r="N149" s="9" t="inlineStr">
-        <is>
-          <t>coa.5010.name</t>
-        </is>
-      </c>
-      <c r="O149" s="10" t="inlineStr">
-        <is>
-          <t>Posted when company-owned product is used on a job.</t>
-        </is>
-      </c>
+      <c r="O149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="9" t="n">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Fertilizer and seed cost of sales</t>
+          <t>Chemical cost of sales (company-owned)</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
@@ -10750,18 +10744,22 @@
       </c>
       <c r="N150" s="9" t="inlineStr">
         <is>
-          <t>coa.5020.name</t>
-        </is>
-      </c>
-      <c r="O150" s="10" t="inlineStr"/>
+          <t>coa.5010.name</t>
+        </is>
+      </c>
+      <c r="O150" s="10" t="inlineStr">
+        <is>
+          <t>Posted when company-owned product is used on a job.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="9" t="n">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>Supplier rebates and early-order discounts</t>
+          <t>Fertilizer and seed cost of sales</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
@@ -10776,14 +10774,10 @@
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr"/>
       <c r="G151" s="9" t="inlineStr">
         <is>
           <t>All</t>
@@ -10796,7 +10790,7 @@
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Chemical Inventory</t>
         </is>
       </c>
       <c r="J151" s="9" t="inlineStr">
@@ -10821,22 +10815,18 @@
       </c>
       <c r="N151" s="9" t="inlineStr">
         <is>
-          <t>coa.5030.name</t>
-        </is>
-      </c>
-      <c r="O151" s="10" t="inlineStr">
-        <is>
-          <t>Reduces chemical cost.</t>
-        </is>
-      </c>
+          <t>coa.5020.name</t>
+        </is>
+      </c>
+      <c r="O151" s="10" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="9" t="n">
-        <v>5100</v>
+        <v>5030</v>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>Aviation fuel and oil</t>
+          <t>Supplier rebates and early-order discounts</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
@@ -10851,10 +10841,14 @@
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr"/>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
           <t>All</t>
@@ -10867,7 +10861,7 @@
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
-          <t>Fuel</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="J152" s="9" t="inlineStr">
@@ -10882,7 +10876,7 @@
       </c>
       <c r="L152" s="9" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="M152" s="9" t="inlineStr">
@@ -10892,22 +10886,22 @@
       </c>
       <c r="N152" s="9" t="inlineStr">
         <is>
-          <t>coa.5100.name</t>
+          <t>coa.5030.name</t>
         </is>
       </c>
       <c r="O152" s="10" t="inlineStr">
         <is>
-          <t>Issued from 1340 per aircraft, per job.</t>
+          <t>Reduces chemical cost.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="9" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>Pilot wages</t>
+          <t>Aviation fuel and oil</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
@@ -10938,7 +10932,7 @@
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="J153" s="9" t="inlineStr">
@@ -10948,12 +10942,12 @@
       </c>
       <c r="K153" s="10" t="inlineStr">
         <is>
-          <t>Cost of labor - COS</t>
+          <t>Supplies &amp; Materials - COGS</t>
         </is>
       </c>
       <c r="L153" s="9" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="M153" s="9" t="inlineStr">
@@ -10963,18 +10957,22 @@
       </c>
       <c r="N153" s="9" t="inlineStr">
         <is>
-          <t>coa.5200.name</t>
-        </is>
-      </c>
-      <c r="O153" s="10" t="inlineStr"/>
+          <t>coa.5100.name</t>
+        </is>
+      </c>
+      <c r="O153" s="10" t="inlineStr">
+        <is>
+          <t>Issued from 1340 per aircraft, per job.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="9" t="n">
-        <v>5210</v>
+        <v>5200</v>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>Loader and ground crew wages</t>
+          <t>Pilot wages</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
@@ -11030,18 +11028,18 @@
       </c>
       <c r="N154" s="9" t="inlineStr">
         <is>
-          <t>coa.5210.name</t>
+          <t>coa.5200.name</t>
         </is>
       </c>
       <c r="O154" s="10" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="9" t="n">
-        <v>5220</v>
+        <v>5210</v>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Maintenance labour – AMEs and mechanics</t>
+          <t>Loader and ground crew wages</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -11097,22 +11095,18 @@
       </c>
       <c r="N155" s="9" t="inlineStr">
         <is>
-          <t>coa.5220.name</t>
-        </is>
-      </c>
-      <c r="O155" s="10" t="inlineStr">
-        <is>
-          <t>Allocated to aircraft or vehicles through Maintenance Orders.</t>
-        </is>
-      </c>
+          <t>coa.5210.name</t>
+        </is>
+      </c>
+      <c r="O155" s="10" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="9" t="n">
-        <v>5250</v>
+        <v>5220</v>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>Direct payroll burden – CPP/QPP and EI/QPIP</t>
+          <t>Maintenance labour – AMEs and mechanics</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
@@ -11133,7 +11127,7 @@
       <c r="F156" s="9" t="inlineStr"/>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr">
@@ -11158,32 +11152,32 @@
       </c>
       <c r="L156" s="9" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="M156" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 (1125-A)</t>
         </is>
       </c>
       <c r="N156" s="9" t="inlineStr">
         <is>
-          <t>coa.5250.name</t>
+          <t>coa.5220.name</t>
         </is>
       </c>
       <c r="O156" s="10" t="inlineStr">
         <is>
-          <t>Employer share, Canada.</t>
+          <t>Allocated to aircraft or vehicles through Maintenance Orders.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="9" t="n">
-        <v>5255</v>
+        <v>5250</v>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>Direct payroll burden – FICA, FUTA and SUTA</t>
+          <t>Direct payroll burden – CPP/QPP and EI/QPIP</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
@@ -11204,7 +11198,7 @@
       <c r="F157" s="9" t="inlineStr"/>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H157" s="9" t="inlineStr">
@@ -11229,32 +11223,32 @@
       </c>
       <c r="L157" s="9" t="inlineStr">
         <is>
+          <t>8350</t>
+        </is>
+      </c>
+      <c r="M157" s="9" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M157" s="9" t="inlineStr">
-        <is>
-          <t>2 (1125-A)</t>
-        </is>
-      </c>
       <c r="N157" s="9" t="inlineStr">
         <is>
-          <t>coa.5255.name</t>
+          <t>coa.5250.name</t>
         </is>
       </c>
       <c r="O157" s="10" t="inlineStr">
         <is>
-          <t>Employer share, US.</t>
+          <t>Employer share, Canada.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="9" t="n">
-        <v>5260</v>
+        <v>5255</v>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>Direct payroll burden – employer health tax and workers’ compensation</t>
+          <t>Direct payroll burden – FICA, FUTA and SUTA</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
@@ -11275,7 +11269,7 @@
       <c r="F158" s="9" t="inlineStr"/>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr">
@@ -11300,7 +11294,7 @@
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M158" s="9" t="inlineStr">
@@ -11310,18 +11304,22 @@
       </c>
       <c r="N158" s="9" t="inlineStr">
         <is>
-          <t>coa.5260.name</t>
-        </is>
-      </c>
-      <c r="O158" s="10" t="inlineStr"/>
+          <t>coa.5255.name</t>
+        </is>
+      </c>
+      <c r="O158" s="10" t="inlineStr">
+        <is>
+          <t>Employer share, US.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="9" t="n">
-        <v>5265</v>
+        <v>5260</v>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>Direct payroll burden – benefits and retirement contributions</t>
+          <t>Direct payroll burden – employer health tax and workers’ compensation</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -11377,18 +11375,18 @@
       </c>
       <c r="N159" s="9" t="inlineStr">
         <is>
-          <t>coa.5265.name</t>
+          <t>coa.5260.name</t>
         </is>
       </c>
       <c r="O159" s="10" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="9" t="n">
-        <v>5270</v>
+        <v>5265</v>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Direct payroll – vacation and statutory holiday pay</t>
+          <t>Direct payroll burden – benefits and retirement contributions</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
@@ -11434,7 +11432,7 @@
       </c>
       <c r="L160" s="9" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="M160" s="9" t="inlineStr">
@@ -11444,18 +11442,18 @@
       </c>
       <c r="N160" s="9" t="inlineStr">
         <is>
-          <t>coa.5270.name</t>
+          <t>coa.5265.name</t>
         </is>
       </c>
       <c r="O160" s="10" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="n">
-        <v>5300</v>
+        <v>5270</v>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – parts issued</t>
+          <t>Direct payroll – vacation and statutory holiday pay</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -11486,7 +11484,7 @@
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
-          <t>Maintenance Orders</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="J161" s="9" t="inlineStr">
@@ -11496,12 +11494,12 @@
       </c>
       <c r="K161" s="10" t="inlineStr">
         <is>
-          <t>Other Costs of Services - COS</t>
+          <t>Cost of labor - COS</t>
         </is>
       </c>
       <c r="L161" s="9" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="M161" s="9" t="inlineStr">
@@ -11511,22 +11509,18 @@
       </c>
       <c r="N161" s="9" t="inlineStr">
         <is>
-          <t>coa.5300.name</t>
-        </is>
-      </c>
-      <c r="O161" s="10" t="inlineStr">
-        <is>
-          <t>Issued from 1310 to a Maintenance Order; AirAg Ops keeps aircraft detail.</t>
-        </is>
-      </c>
+          <t>coa.5270.name</t>
+        </is>
+      </c>
+      <c r="O161" s="10" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="n">
-        <v>5310</v>
+        <v>5300</v>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – outside services</t>
+          <t>Aircraft maintenance – parts issued</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
@@ -11582,22 +11576,22 @@
       </c>
       <c r="N162" s="9" t="inlineStr">
         <is>
-          <t>coa.5310.name</t>
+          <t>coa.5300.name</t>
         </is>
       </c>
       <c r="O162" s="10" t="inlineStr">
         <is>
-          <t>Sublet repairs.</t>
+          <t>Issued from 1310 to a Maintenance Order; AirAg Ops keeps aircraft detail.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9" t="n">
-        <v>5320</v>
+        <v>5310</v>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – engine and propeller overhauls (expensed)</t>
+          <t>Aircraft maintenance – outside services</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
@@ -11653,22 +11647,22 @@
       </c>
       <c r="N163" s="9" t="inlineStr">
         <is>
-          <t>coa.5320.name</t>
+          <t>coa.5310.name</t>
         </is>
       </c>
       <c r="O163" s="10" t="inlineStr">
         <is>
-          <t>Capitalized overhauls go to 1670/1620 instead.</t>
+          <t>Sublet repairs.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="9" t="n">
-        <v>5330</v>
+        <v>5320</v>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – components, avionics and dispersal systems</t>
+          <t>Aircraft maintenance – engine and propeller overhauls (expensed)</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
@@ -11724,18 +11718,22 @@
       </c>
       <c r="N164" s="9" t="inlineStr">
         <is>
-          <t>coa.5330.name</t>
-        </is>
-      </c>
-      <c r="O164" s="10" t="inlineStr"/>
+          <t>coa.5320.name</t>
+        </is>
+      </c>
+      <c r="O164" s="10" t="inlineStr">
+        <is>
+          <t>Capitalized overhauls go to 1670/1620 instead.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="9" t="n">
-        <v>5340</v>
+        <v>5330</v>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – shop consumables</t>
+          <t>Aircraft maintenance – components, avionics and dispersal systems</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
@@ -11791,18 +11789,18 @@
       </c>
       <c r="N165" s="9" t="inlineStr">
         <is>
-          <t>coa.5340.name</t>
+          <t>coa.5330.name</t>
         </is>
       </c>
       <c r="O165" s="10" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="9" t="n">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Aircraft hull insurance</t>
+          <t>Aircraft maintenance – shop consumables</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
@@ -11833,7 +11831,7 @@
       </c>
       <c r="I166" s="9" t="inlineStr">
         <is>
-          <t>Fleet – Aircraft</t>
+          <t>Maintenance Orders</t>
         </is>
       </c>
       <c r="J166" s="9" t="inlineStr">
@@ -11848,7 +11846,7 @@
       </c>
       <c r="L166" s="9" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="M166" s="9" t="inlineStr">
@@ -11858,18 +11856,18 @@
       </c>
       <c r="N166" s="9" t="inlineStr">
         <is>
-          <t>coa.5400.name</t>
+          <t>coa.5340.name</t>
         </is>
       </c>
       <c r="O166" s="10" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="9" t="n">
-        <v>5410</v>
+        <v>5400</v>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Aviation and aerial application liability insurance</t>
+          <t>Aircraft hull insurance</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -11925,22 +11923,18 @@
       </c>
       <c r="N167" s="9" t="inlineStr">
         <is>
-          <t>coa.5410.name</t>
-        </is>
-      </c>
-      <c r="O167" s="10" t="inlineStr">
-        <is>
-          <t>Includes chemical trespass / pollution liability.</t>
-        </is>
-      </c>
+          <t>coa.5400.name</t>
+        </is>
+      </c>
+      <c r="O167" s="10" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="9" t="n">
-        <v>5500</v>
+        <v>5410</v>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Aircraft leases and rentals</t>
+          <t>Aviation and aerial application liability insurance</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
@@ -11981,12 +11975,12 @@
       </c>
       <c r="K168" s="10" t="inlineStr">
         <is>
-          <t>Equipment Rental - COS</t>
+          <t>Other Costs of Services - COS</t>
         </is>
       </c>
       <c r="L168" s="9" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="M168" s="9" t="inlineStr">
@@ -11996,18 +11990,22 @@
       </c>
       <c r="N168" s="9" t="inlineStr">
         <is>
-          <t>coa.5500.name</t>
-        </is>
-      </c>
-      <c r="O168" s="10" t="inlineStr"/>
+          <t>coa.5410.name</t>
+        </is>
+      </c>
+      <c r="O168" s="10" t="inlineStr">
+        <is>
+          <t>Includes chemical trespass / pollution liability.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="9" t="n">
-        <v>5510</v>
+        <v>5500</v>
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>Hangar, tie-down and landing fees</t>
+          <t>Aircraft leases and rentals</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
@@ -12038,7 +12036,7 @@
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Fleet – Aircraft</t>
         </is>
       </c>
       <c r="J169" s="9" t="inlineStr">
@@ -12048,12 +12046,12 @@
       </c>
       <c r="K169" s="10" t="inlineStr">
         <is>
-          <t>Other Costs of Services - COS</t>
+          <t>Equipment Rental - COS</t>
         </is>
       </c>
       <c r="L169" s="9" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="M169" s="9" t="inlineStr">
@@ -12063,18 +12061,18 @@
       </c>
       <c r="N169" s="9" t="inlineStr">
         <is>
-          <t>coa.5510.name</t>
+          <t>coa.5500.name</t>
         </is>
       </c>
       <c r="O169" s="10" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="9" t="n">
-        <v>5600</v>
+        <v>5510</v>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>GPS, guidance and flight-tracking subscriptions</t>
+          <t>Hangar, tie-down and landing fees</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
@@ -12120,7 +12118,7 @@
       </c>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="M170" s="9" t="inlineStr">
@@ -12130,22 +12128,18 @@
       </c>
       <c r="N170" s="9" t="inlineStr">
         <is>
-          <t>coa.5600.name</t>
-        </is>
-      </c>
-      <c r="O170" s="10" t="inlineStr">
-        <is>
-          <t>Correction services, data plans, AirAg Link.</t>
-        </is>
-      </c>
+          <t>coa.5510.name</t>
+        </is>
+      </c>
+      <c r="O170" s="10" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="9" t="n">
-        <v>5610</v>
+        <v>5600</v>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Crew travel, lodging and per diem</t>
+          <t>GPS, guidance and flight-tracking subscriptions</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -12191,7 +12185,7 @@
       </c>
       <c r="L171" s="9" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="M171" s="9" t="inlineStr">
@@ -12201,22 +12195,22 @@
       </c>
       <c r="N171" s="9" t="inlineStr">
         <is>
-          <t>coa.5610.name</t>
+          <t>coa.5600.name</t>
         </is>
       </c>
       <c r="O171" s="10" t="inlineStr">
         <is>
-          <t>Field and seasonal deployments.</t>
+          <t>Correction services, data plans, AirAg Link.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="9" t="n">
-        <v>5620</v>
+        <v>5610</v>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Ground support vehicle fuel</t>
+          <t>Crew travel, lodging and per diem</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -12247,7 +12241,7 @@
       </c>
       <c r="I172" s="9" t="inlineStr">
         <is>
-          <t>Fuel</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="J172" s="9" t="inlineStr">
@@ -12262,7 +12256,7 @@
       </c>
       <c r="L172" s="9" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="M172" s="9" t="inlineStr">
@@ -12272,18 +12266,22 @@
       </c>
       <c r="N172" s="9" t="inlineStr">
         <is>
-          <t>coa.5620.name</t>
-        </is>
-      </c>
-      <c r="O172" s="10" t="inlineStr"/>
+          <t>coa.5610.name</t>
+        </is>
+      </c>
+      <c r="O172" s="10" t="inlineStr">
+        <is>
+          <t>Field and seasonal deployments.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="9" t="n">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Vehicle and equipment maintenance – parts issued</t>
+          <t>Ground support vehicle fuel</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -12314,7 +12312,7 @@
       </c>
       <c r="I173" s="9" t="inlineStr">
         <is>
-          <t>Maintenance Orders</t>
+          <t>Fuel</t>
         </is>
       </c>
       <c r="J173" s="9" t="inlineStr">
@@ -12329,7 +12327,7 @@
       </c>
       <c r="L173" s="9" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="M173" s="9" t="inlineStr">
@@ -12339,22 +12337,18 @@
       </c>
       <c r="N173" s="9" t="inlineStr">
         <is>
-          <t>coa.5630.name</t>
-        </is>
-      </c>
-      <c r="O173" s="10" t="inlineStr">
-        <is>
-          <t>Issued from 1320 to a Maintenance Order.</t>
-        </is>
-      </c>
+          <t>coa.5620.name</t>
+        </is>
+      </c>
+      <c r="O173" s="10" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="9" t="n">
-        <v>5640</v>
+        <v>5630</v>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Vehicle and equipment maintenance – outside services</t>
+          <t>Vehicle and equipment maintenance – parts issued</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -12410,18 +12404,22 @@
       </c>
       <c r="N174" s="9" t="inlineStr">
         <is>
-          <t>coa.5640.name</t>
-        </is>
-      </c>
-      <c r="O174" s="10" t="inlineStr"/>
+          <t>coa.5630.name</t>
+        </is>
+      </c>
+      <c r="O174" s="10" t="inlineStr">
+        <is>
+          <t>Issued from 1320 to a Maintenance Order.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="9" t="n">
-        <v>5650</v>
+        <v>5640</v>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Equipment and vehicle rentals</t>
+          <t>Vehicle and equipment maintenance – outside services</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -12452,7 +12450,7 @@
       </c>
       <c r="I175" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Maintenance Orders</t>
         </is>
       </c>
       <c r="J175" s="9" t="inlineStr">
@@ -12462,12 +12460,12 @@
       </c>
       <c r="K175" s="10" t="inlineStr">
         <is>
-          <t>Equipment Rental - COS</t>
+          <t>Other Costs of Services - COS</t>
         </is>
       </c>
       <c r="L175" s="9" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="M175" s="9" t="inlineStr">
@@ -12477,18 +12475,18 @@
       </c>
       <c r="N175" s="9" t="inlineStr">
         <is>
-          <t>coa.5650.name</t>
+          <t>coa.5640.name</t>
         </is>
       </c>
       <c r="O175" s="10" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="9" t="n">
-        <v>5700</v>
+        <v>5650</v>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>Subcontracted aerial application</t>
+          <t>Equipment and vehicle rentals</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -12529,12 +12527,12 @@
       </c>
       <c r="K176" s="10" t="inlineStr">
         <is>
-          <t>Other Costs of Services - COS</t>
+          <t>Equipment Rental - COS</t>
         </is>
       </c>
       <c r="L176" s="9" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="M176" s="9" t="inlineStr">
@@ -12544,18 +12542,18 @@
       </c>
       <c r="N176" s="9" t="inlineStr">
         <is>
-          <t>coa.5700.name</t>
+          <t>coa.5650.name</t>
         </is>
       </c>
       <c r="O176" s="10" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="9" t="n">
-        <v>5710</v>
+        <v>5700</v>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>Containment, rinsate and disposal costs</t>
+          <t>Subcontracted aerial application</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -12586,7 +12584,7 @@
       </c>
       <c r="I177" s="9" t="inlineStr">
         <is>
-          <t>Chemical Inventory</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="J177" s="9" t="inlineStr">
@@ -12601,7 +12599,7 @@
       </c>
       <c r="L177" s="9" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="M177" s="9" t="inlineStr">
@@ -12611,18 +12609,18 @@
       </c>
       <c r="N177" s="9" t="inlineStr">
         <is>
-          <t>coa.5710.name</t>
+          <t>coa.5700.name</t>
         </is>
       </c>
       <c r="O177" s="10" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="9" t="n">
-        <v>5800</v>
+        <v>5710</v>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Amortization – aircraft</t>
+          <t>Containment, rinsate and disposal costs</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -12653,7 +12651,7 @@
       </c>
       <c r="I178" s="9" t="inlineStr">
         <is>
-          <t>Fixed Assets</t>
+          <t>Chemical Inventory</t>
         </is>
       </c>
       <c r="J178" s="9" t="inlineStr">
@@ -12668,7 +12666,7 @@
       </c>
       <c r="L178" s="9" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="M178" s="9" t="inlineStr">
@@ -12678,18 +12676,18 @@
       </c>
       <c r="N178" s="9" t="inlineStr">
         <is>
-          <t>coa.5800.name</t>
+          <t>coa.5710.name</t>
         </is>
       </c>
       <c r="O178" s="10" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="9" t="n">
-        <v>5810</v>
+        <v>5800</v>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Amortization – vehicles and ground equipment</t>
+          <t>Amortization – aircraft</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -12745,18 +12743,18 @@
       </c>
       <c r="N179" s="9" t="inlineStr">
         <is>
-          <t>coa.5810.name</t>
+          <t>coa.5800.name</t>
         </is>
       </c>
       <c r="O179" s="10" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="9" t="n">
-        <v>5900</v>
+        <v>5810</v>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Inventory adjustments – parts</t>
+          <t>Amortization – vehicles and ground equipment</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
@@ -12787,7 +12785,7 @@
       </c>
       <c r="I180" s="9" t="inlineStr">
         <is>
-          <t>Parts Store</t>
+          <t>Fixed Assets</t>
         </is>
       </c>
       <c r="J180" s="9" t="inlineStr">
@@ -12797,12 +12795,12 @@
       </c>
       <c r="K180" s="10" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials - COGS</t>
+          <t>Other Costs of Services - COS</t>
         </is>
       </c>
       <c r="L180" s="9" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="M180" s="9" t="inlineStr">
@@ -12812,22 +12810,18 @@
       </c>
       <c r="N180" s="9" t="inlineStr">
         <is>
-          <t>coa.5900.name</t>
-        </is>
-      </c>
-      <c r="O180" s="10" t="inlineStr">
-        <is>
-          <t>Counts, write-downs, obsolescence.</t>
-        </is>
-      </c>
+          <t>coa.5810.name</t>
+        </is>
+      </c>
+      <c r="O180" s="10" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="9" t="n">
-        <v>5910</v>
+        <v>5900</v>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Inventory adjustments – chemicals and fuel</t>
+          <t>Inventory adjustments – parts</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -12858,7 +12852,7 @@
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>Chemical Inventory</t>
+          <t>Parts Store</t>
         </is>
       </c>
       <c r="J181" s="9" t="inlineStr">
@@ -12883,18 +12877,22 @@
       </c>
       <c r="N181" s="9" t="inlineStr">
         <is>
-          <t>coa.5910.name</t>
-        </is>
-      </c>
-      <c r="O181" s="10" t="inlineStr"/>
+          <t>coa.5900.name</t>
+        </is>
+      </c>
+      <c r="O181" s="10" t="inlineStr">
+        <is>
+          <t>Counts, write-downs, obsolescence.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="9" t="n">
-        <v>5920</v>
+        <v>5910</v>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Freight-in, customs and duty</t>
+          <t>Inventory adjustments – chemicals and fuel</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -12925,145 +12923,149 @@
       </c>
       <c r="I182" s="9" t="inlineStr">
         <is>
+          <t>Chemical Inventory</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="K182" s="10" t="inlineStr">
+        <is>
+          <t>Supplies &amp; Materials - COGS</t>
+        </is>
+      </c>
+      <c r="L182" s="9" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="M182" s="9" t="inlineStr">
+        <is>
+          <t>2 (1125-A)</t>
+        </is>
+      </c>
+      <c r="N182" s="9" t="inlineStr">
+        <is>
+          <t>coa.5910.name</t>
+        </is>
+      </c>
+      <c r="O182" s="10" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="n">
+        <v>5920</v>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>Freight-in, customs and duty</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>Postable</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr"/>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>AirAg Ops only</t>
+        </is>
+      </c>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="J182" s="9" t="inlineStr">
+      <c r="J183" s="9" t="inlineStr">
         <is>
           <t>Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="K182" s="10" t="inlineStr">
+      <c r="K183" s="10" t="inlineStr">
         <is>
           <t>Supplies &amp; Materials - COGS</t>
         </is>
       </c>
-      <c r="L182" s="9" t="inlineStr">
+      <c r="L183" s="9" t="inlineStr">
         <is>
           <t>8457</t>
         </is>
       </c>
-      <c r="M182" s="9" t="inlineStr">
+      <c r="M183" s="9" t="inlineStr">
         <is>
           <t>2 (1125-A)</t>
         </is>
       </c>
-      <c r="N182" s="9" t="inlineStr">
+      <c r="N183" s="9" t="inlineStr">
         <is>
           <t>coa.5920.name</t>
         </is>
       </c>
-      <c r="O182" s="10" t="inlineStr">
+      <c r="O183" s="10" t="inlineStr">
         <is>
           <t>Use when not capitalized into inventory cost.</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="7" t="n">
+    <row r="184">
+      <c r="A184" s="7" t="n">
         <v>6000</v>
       </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>Operating and administrative expenses</t>
         </is>
       </c>
-      <c r="C183" s="7" t="inlineStr">
+      <c r="C184" s="7" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D183" s="7" t="inlineStr">
+      <c r="D184" s="7" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="E183" s="7" t="inlineStr"/>
-      <c r="F183" s="7" t="inlineStr"/>
-      <c r="G183" s="7" t="inlineStr"/>
-      <c r="H183" s="7" t="inlineStr"/>
-      <c r="I183" s="7" t="inlineStr"/>
-      <c r="J183" s="7" t="inlineStr"/>
-      <c r="K183" s="8" t="inlineStr"/>
-      <c r="L183" s="7" t="inlineStr"/>
-      <c r="M183" s="7" t="inlineStr"/>
-      <c r="N183" s="7" t="inlineStr">
+      <c r="E184" s="7" t="inlineStr"/>
+      <c r="F184" s="7" t="inlineStr"/>
+      <c r="G184" s="7" t="inlineStr"/>
+      <c r="H184" s="7" t="inlineStr"/>
+      <c r="I184" s="7" t="inlineStr"/>
+      <c r="J184" s="7" t="inlineStr"/>
+      <c r="K184" s="8" t="inlineStr"/>
+      <c r="L184" s="7" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+      <c r="N184" s="7" t="inlineStr">
         <is>
           <t>coa.6000.name</t>
         </is>
       </c>
-      <c r="O183" s="8" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="9" t="n">
-        <v>6010</v>
-      </c>
-      <c r="B184" s="10" t="inlineStr">
-        <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="C184" s="9" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D184" s="9" t="inlineStr">
-        <is>
-          <t>Postable</t>
-        </is>
-      </c>
-      <c r="E184" s="9" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr"/>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H184" s="9" t="inlineStr">
-        <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I184" s="9" t="inlineStr"/>
-      <c r="J184" s="9" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="K184" s="10" t="inlineStr">
-        <is>
-          <t>Advertising/Promotional</t>
-        </is>
-      </c>
-      <c r="L184" s="9" t="inlineStr">
-        <is>
-          <t>8520</t>
-        </is>
-      </c>
-      <c r="M184" s="9" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N184" s="9" t="inlineStr">
-        <is>
-          <t>coa.6010.name</t>
-        </is>
-      </c>
-      <c r="O184" s="10" t="inlineStr"/>
+      <c r="O184" s="8" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="9" t="n">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Trade shows and association events</t>
+          <t>Advertising and promotion</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -13115,18 +13117,18 @@
       </c>
       <c r="N185" s="9" t="inlineStr">
         <is>
-          <t>coa.6020.name</t>
+          <t>coa.6010.name</t>
         </is>
       </c>
       <c r="O185" s="10" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="9" t="n">
-        <v>6100</v>
+        <v>6020</v>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Salaries – management</t>
+          <t>Trade shows and association events</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
@@ -13152,14 +13154,10 @@
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
-          <t>AirAg Ops only</t>
-        </is>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I186" s="9" t="inlineStr"/>
       <c r="J186" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -13167,37 +13165,33 @@
       </c>
       <c r="K186" s="10" t="inlineStr">
         <is>
-          <t>Officers' Compensation</t>
+          <t>Advertising/Promotional</t>
         </is>
       </c>
       <c r="L186" s="9" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="M186" s="9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N186" s="9" t="inlineStr">
         <is>
-          <t>coa.6100.name</t>
-        </is>
-      </c>
-      <c r="O186" s="10" t="inlineStr">
-        <is>
-          <t>Shareholder-managers and officers.</t>
-        </is>
-      </c>
+          <t>coa.6020.name</t>
+        </is>
+      </c>
+      <c r="O186" s="10" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="9" t="n">
-        <v>6110</v>
+        <v>6100</v>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Salaries – office and dispatch staff</t>
+          <t>Salaries – management</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -13238,7 +13232,7 @@
       </c>
       <c r="K187" s="10" t="inlineStr">
         <is>
-          <t>Payroll Expenses</t>
+          <t>Officers' Compensation</t>
         </is>
       </c>
       <c r="L187" s="9" t="inlineStr">
@@ -13248,23 +13242,27 @@
       </c>
       <c r="M187" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N187" s="9" t="inlineStr">
         <is>
-          <t>coa.6110.name</t>
-        </is>
-      </c>
-      <c r="O187" s="10" t="inlineStr"/>
+          <t>coa.6100.name</t>
+        </is>
+      </c>
+      <c r="O187" s="10" t="inlineStr">
+        <is>
+          <t>Shareholder-managers and officers.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="9" t="n">
-        <v>6150</v>
+        <v>6110</v>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Payroll burden – CPP/QPP and EI/QPIP</t>
+          <t>Salaries – office and dispatch staff</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
@@ -13285,7 +13283,7 @@
       <c r="F188" s="9" t="inlineStr"/>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H188" s="9" t="inlineStr">
@@ -13310,28 +13308,28 @@
       </c>
       <c r="L188" s="9" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="M188" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N188" s="9" t="inlineStr">
         <is>
-          <t>coa.6150.name</t>
+          <t>coa.6110.name</t>
         </is>
       </c>
       <c r="O188" s="10" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="9" t="n">
-        <v>6155</v>
+        <v>6150</v>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Payroll burden – FICA, FUTA and SUTA</t>
+          <t>Payroll burden – CPP/QPP and EI/QPIP</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
@@ -13352,7 +13350,7 @@
       <c r="F189" s="9" t="inlineStr"/>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -13377,28 +13375,28 @@
       </c>
       <c r="L189" s="9" t="inlineStr">
         <is>
+          <t>8622</t>
+        </is>
+      </c>
+      <c r="M189" s="9" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M189" s="9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="N189" s="9" t="inlineStr">
         <is>
-          <t>coa.6155.name</t>
+          <t>coa.6150.name</t>
         </is>
       </c>
       <c r="O189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="9" t="n">
-        <v>6160</v>
+        <v>6155</v>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Payroll burden – employer health tax and workers’ compensation</t>
+          <t>Payroll burden – FICA, FUTA and SUTA</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
@@ -13419,7 +13417,7 @@
       <c r="F190" s="9" t="inlineStr"/>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr">
@@ -13444,28 +13442,28 @@
       </c>
       <c r="L190" s="9" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M190" s="9" t="inlineStr">
         <is>
-          <t>17 / 26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N190" s="9" t="inlineStr">
         <is>
-          <t>coa.6160.name</t>
+          <t>coa.6155.name</t>
         </is>
       </c>
       <c r="O190" s="10" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="9" t="n">
-        <v>6165</v>
+        <v>6160</v>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Benefits and retirement plan contributions</t>
+          <t>Payroll burden – employer health tax and workers’ compensation</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
@@ -13511,28 +13509,28 @@
       </c>
       <c r="L191" s="9" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="M191" s="9" t="inlineStr">
         <is>
-          <t>23 / 24</t>
+          <t>17 / 26</t>
         </is>
       </c>
       <c r="N191" s="9" t="inlineStr">
         <is>
-          <t>coa.6165.name</t>
+          <t>coa.6160.name</t>
         </is>
       </c>
       <c r="O191" s="10" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="9" t="n">
-        <v>6170</v>
+        <v>6165</v>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Vacation and statutory holiday pay – administration</t>
+          <t>Benefits and retirement plan contributions</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
@@ -13578,28 +13576,28 @@
       </c>
       <c r="L192" s="9" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="M192" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23 / 24</t>
         </is>
       </c>
       <c r="N192" s="9" t="inlineStr">
         <is>
-          <t>coa.6170.name</t>
+          <t>coa.6165.name</t>
         </is>
       </c>
       <c r="O192" s="10" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="9" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>Insurance – general liability, property and vehicles</t>
+          <t>Vacation and statutory holiday pay – administration</t>
         </is>
       </c>
       <c r="C193" s="9" t="inlineStr">
@@ -13625,10 +13623,14 @@
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I193" s="9" t="inlineStr"/>
+          <t>AirAg Ops only</t>
+        </is>
+      </c>
+      <c r="I193" s="9" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
       <c r="J193" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -13636,33 +13638,33 @@
       </c>
       <c r="K193" s="10" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payroll Expenses</t>
         </is>
       </c>
       <c r="L193" s="9" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="M193" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
         <is>
-          <t>coa.6200.name</t>
+          <t>coa.6170.name</t>
         </is>
       </c>
       <c r="O193" s="10" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="9" t="n">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>Rent – office, hangar and storage</t>
+          <t>Insurance – general liability, property and vehicles</t>
         </is>
       </c>
       <c r="C194" s="9" t="inlineStr">
@@ -13699,33 +13701,33 @@
       </c>
       <c r="K194" s="10" t="inlineStr">
         <is>
-          <t>Rent or Lease of Buildings</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="L194" s="9" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="M194" s="9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N194" s="9" t="inlineStr">
         <is>
-          <t>coa.6300.name</t>
+          <t>coa.6200.name</t>
         </is>
       </c>
       <c r="O194" s="10" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="9" t="n">
-        <v>6310</v>
+        <v>6300</v>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent – office, hangar and storage</t>
         </is>
       </c>
       <c r="C195" s="9" t="inlineStr">
@@ -13762,33 +13764,33 @@
       </c>
       <c r="K195" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent or Lease of Buildings</t>
         </is>
       </c>
       <c r="L195" s="9" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="M195" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
         <is>
-          <t>coa.6310.name</t>
+          <t>coa.6300.name</t>
         </is>
       </c>
       <c r="O195" s="10" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="9" t="n">
-        <v>6320</v>
+        <v>6310</v>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>Telephone, internet and satellite communications</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
@@ -13830,7 +13832,7 @@
       </c>
       <c r="L196" s="9" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="M196" s="9" t="inlineStr">
@@ -13840,18 +13842,18 @@
       </c>
       <c r="N196" s="9" t="inlineStr">
         <is>
-          <t>coa.6320.name</t>
+          <t>coa.6310.name</t>
         </is>
       </c>
       <c r="O196" s="10" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="9" t="n">
-        <v>6330</v>
+        <v>6320</v>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>Property taxes</t>
+          <t>Telephone, internet and satellite communications</t>
         </is>
       </c>
       <c r="C197" s="9" t="inlineStr">
@@ -13888,33 +13890,33 @@
       </c>
       <c r="K197" s="10" t="inlineStr">
         <is>
-          <t>Taxes Paid</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L197" s="9" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="M197" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N197" s="9" t="inlineStr">
         <is>
-          <t>coa.6330.name</t>
+          <t>coa.6320.name</t>
         </is>
       </c>
       <c r="O197" s="10" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="9" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>Repairs and maintenance – buildings and hangars</t>
+          <t>Property taxes</t>
         </is>
       </c>
       <c r="C198" s="9" t="inlineStr">
@@ -13940,14 +13942,10 @@
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>AirAg Ops only</t>
-        </is>
-      </c>
-      <c r="I198" s="9" t="inlineStr">
-        <is>
-          <t>Maintenance Orders</t>
-        </is>
-      </c>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I198" s="9" t="inlineStr"/>
       <c r="J198" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -13955,33 +13953,33 @@
       </c>
       <c r="K198" s="10" t="inlineStr">
         <is>
-          <t>Repair &amp; Maintenance</t>
+          <t>Taxes Paid</t>
         </is>
       </c>
       <c r="L198" s="9" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="M198" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N198" s="9" t="inlineStr">
         <is>
-          <t>coa.6340.name</t>
+          <t>coa.6330.name</t>
         </is>
       </c>
       <c r="O198" s="10" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="9" t="n">
-        <v>6350</v>
+        <v>6340</v>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>Repairs and maintenance – airstrips, yards and containment</t>
+          <t>Repairs and maintenance – buildings and hangars</t>
         </is>
       </c>
       <c r="C199" s="9" t="inlineStr">
@@ -14027,7 +14025,7 @@
       </c>
       <c r="L199" s="9" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="M199" s="9" t="inlineStr">
@@ -14037,18 +14035,18 @@
       </c>
       <c r="N199" s="9" t="inlineStr">
         <is>
-          <t>coa.6350.name</t>
+          <t>coa.6340.name</t>
         </is>
       </c>
       <c r="O199" s="10" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="9" t="n">
-        <v>6400</v>
+        <v>6350</v>
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Repairs and maintenance – airstrips, yards and containment</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
@@ -14074,10 +14072,14 @@
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I200" s="9" t="inlineStr"/>
+          <t>AirAg Ops only</t>
+        </is>
+      </c>
+      <c r="I200" s="9" t="inlineStr">
+        <is>
+          <t>Maintenance Orders</t>
+        </is>
+      </c>
       <c r="J200" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -14085,33 +14087,33 @@
       </c>
       <c r="K200" s="10" t="inlineStr">
         <is>
-          <t>Legal &amp; Professional Fees</t>
+          <t>Repair &amp; Maintenance</t>
         </is>
       </c>
       <c r="L200" s="9" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="M200" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N200" s="9" t="inlineStr">
         <is>
-          <t>coa.6400.name</t>
+          <t>coa.6350.name</t>
         </is>
       </c>
       <c r="O200" s="10" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="9" t="n">
-        <v>6410</v>
+        <v>6400</v>
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>Accounting and audit fees</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="C201" s="9" t="inlineStr">
@@ -14153,7 +14155,7 @@
       </c>
       <c r="L201" s="9" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="M201" s="9" t="inlineStr">
@@ -14163,18 +14165,18 @@
       </c>
       <c r="N201" s="9" t="inlineStr">
         <is>
-          <t>coa.6410.name</t>
+          <t>coa.6400.name</t>
         </is>
       </c>
       <c r="O201" s="10" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="9" t="n">
-        <v>6420</v>
+        <v>6410</v>
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>Consulting and professional fees</t>
+          <t>Accounting and audit fees</t>
         </is>
       </c>
       <c r="C202" s="9" t="inlineStr">
@@ -14216,7 +14218,7 @@
       </c>
       <c r="L202" s="9" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="M202" s="9" t="inlineStr">
@@ -14226,18 +14228,18 @@
       </c>
       <c r="N202" s="9" t="inlineStr">
         <is>
-          <t>coa.6420.name</t>
+          <t>coa.6410.name</t>
         </is>
       </c>
       <c r="O202" s="10" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="9" t="n">
-        <v>6500</v>
+        <v>6420</v>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Aviation certificates and regulatory fees (TC / FAA)</t>
+          <t>Consulting and professional fees</t>
         </is>
       </c>
       <c r="C203" s="9" t="inlineStr">
@@ -14274,37 +14276,33 @@
       </c>
       <c r="K203" s="10" t="inlineStr">
         <is>
-          <t>Taxes Paid</t>
+          <t>Legal &amp; Professional Fees</t>
         </is>
       </c>
       <c r="L203" s="9" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="M203" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N203" s="9" t="inlineStr">
         <is>
-          <t>coa.6500.name</t>
-        </is>
-      </c>
-      <c r="O203" s="10" t="inlineStr">
-        <is>
-          <t>Air operator certificate, aircraft registration, AMO approvals.</t>
-        </is>
-      </c>
+          <t>coa.6420.name</t>
+        </is>
+      </c>
+      <c r="O203" s="10" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="9" t="n">
-        <v>6510</v>
+        <v>6500</v>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>Pesticide applicator licences, permits and registrations</t>
+          <t>Aviation certificates and regulatory fees (TC / FAA)</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
@@ -14356,22 +14354,22 @@
       </c>
       <c r="N204" s="9" t="inlineStr">
         <is>
-          <t>coa.6510.name</t>
+          <t>coa.6500.name</t>
         </is>
       </c>
       <c r="O204" s="10" t="inlineStr">
         <is>
-          <t>Provincial / state applicator and operator licences.</t>
+          <t>Air operator certificate, aircraft registration, AMO approvals.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="9" t="n">
-        <v>6520</v>
+        <v>6510</v>
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>Memberships and associations</t>
+          <t>Pesticide applicator licences, permits and registrations</t>
         </is>
       </c>
       <c r="C205" s="9" t="inlineStr">
@@ -14408,37 +14406,37 @@
       </c>
       <c r="K205" s="10" t="inlineStr">
         <is>
-          <t>Dues &amp; Subscriptions</t>
+          <t>Taxes Paid</t>
         </is>
       </c>
       <c r="L205" s="9" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="M205" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N205" s="9" t="inlineStr">
         <is>
-          <t>coa.6520.name</t>
+          <t>coa.6510.name</t>
         </is>
       </c>
       <c r="O205" s="10" t="inlineStr">
         <is>
-          <t>E.g. CAAA, NAAA, provincial and state associations.</t>
+          <t>Provincial / state applicator and operator licences.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="9" t="n">
-        <v>6530</v>
+        <v>6520</v>
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>Training and recurrent training</t>
+          <t>Memberships and associations</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
@@ -14475,12 +14473,12 @@
       </c>
       <c r="K206" s="10" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Service Cost</t>
+          <t>Dues &amp; Subscriptions</t>
         </is>
       </c>
       <c r="L206" s="9" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="M206" s="9" t="inlineStr">
@@ -14490,22 +14488,22 @@
       </c>
       <c r="N206" s="9" t="inlineStr">
         <is>
-          <t>coa.6530.name</t>
+          <t>coa.6520.name</t>
         </is>
       </c>
       <c r="O206" s="10" t="inlineStr">
         <is>
-          <t>Pilot proficiency, PAASS, safety and dangerous goods training.</t>
+          <t>E.g. CAAA, NAAA, provincial and state associations.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="9" t="n">
-        <v>6540</v>
+        <v>6530</v>
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>Safety equipment, PPE and environmental compliance</t>
+          <t>Training and recurrent training</t>
         </is>
       </c>
       <c r="C207" s="9" t="inlineStr">
@@ -14542,12 +14540,12 @@
       </c>
       <c r="K207" s="10" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials</t>
+          <t>Other Miscellaneous Service Cost</t>
         </is>
       </c>
       <c r="L207" s="9" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="M207" s="9" t="inlineStr">
@@ -14557,18 +14555,22 @@
       </c>
       <c r="N207" s="9" t="inlineStr">
         <is>
-          <t>coa.6540.name</t>
-        </is>
-      </c>
-      <c r="O207" s="10" t="inlineStr"/>
+          <t>coa.6530.name</t>
+        </is>
+      </c>
+      <c r="O207" s="10" t="inlineStr">
+        <is>
+          <t>Pilot proficiency, PAASS, safety and dangerous goods training.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="9" t="n">
-        <v>6600</v>
+        <v>6540</v>
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>Office supplies and postage</t>
+          <t>Safety equipment, PPE and environmental compliance</t>
         </is>
       </c>
       <c r="C208" s="9" t="inlineStr">
@@ -14605,12 +14607,12 @@
       </c>
       <c r="K208" s="10" t="inlineStr">
         <is>
-          <t>Office/General Administrative Expenses</t>
+          <t>Supplies &amp; Materials</t>
         </is>
       </c>
       <c r="L208" s="9" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="M208" s="9" t="inlineStr">
@@ -14620,18 +14622,18 @@
       </c>
       <c r="N208" s="9" t="inlineStr">
         <is>
-          <t>coa.6600.name</t>
+          <t>coa.6540.name</t>
         </is>
       </c>
       <c r="O208" s="10" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="9" t="n">
-        <v>6610</v>
+        <v>6600</v>
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>Software and subscriptions</t>
+          <t>Office supplies and postage</t>
         </is>
       </c>
       <c r="C209" s="9" t="inlineStr">
@@ -14668,12 +14670,12 @@
       </c>
       <c r="K209" s="10" t="inlineStr">
         <is>
-          <t>Dues &amp; Subscriptions</t>
+          <t>Office/General Administrative Expenses</t>
         </is>
       </c>
       <c r="L209" s="9" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="M209" s="9" t="inlineStr">
@@ -14683,22 +14685,18 @@
       </c>
       <c r="N209" s="9" t="inlineStr">
         <is>
-          <t>coa.6610.name</t>
-        </is>
-      </c>
-      <c r="O209" s="10" t="inlineStr">
-        <is>
-          <t>AirAg Ops, accounting and payroll subscriptions.</t>
-        </is>
-      </c>
+          <t>coa.6600.name</t>
+        </is>
+      </c>
+      <c r="O209" s="10" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="9" t="n">
-        <v>6620</v>
+        <v>6610</v>
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>Bank service charges</t>
+          <t>Software and subscriptions</t>
         </is>
       </c>
       <c r="C210" s="9" t="inlineStr">
@@ -14735,12 +14733,12 @@
       </c>
       <c r="K210" s="10" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Dues &amp; Subscriptions</t>
         </is>
       </c>
       <c r="L210" s="9" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="M210" s="9" t="inlineStr">
@@ -14750,18 +14748,22 @@
       </c>
       <c r="N210" s="9" t="inlineStr">
         <is>
-          <t>coa.6620.name</t>
-        </is>
-      </c>
-      <c r="O210" s="10" t="inlineStr"/>
+          <t>coa.6610.name</t>
+        </is>
+      </c>
+      <c r="O210" s="10" t="inlineStr">
+        <is>
+          <t>AirAg Ops, accounting and payroll subscriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="9" t="n">
-        <v>6630</v>
+        <v>6620</v>
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>Merchant and credit card fees</t>
+          <t>Bank service charges</t>
         </is>
       </c>
       <c r="C211" s="9" t="inlineStr">
@@ -14803,7 +14805,7 @@
       </c>
       <c r="L211" s="9" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="M211" s="9" t="inlineStr">
@@ -14813,18 +14815,18 @@
       </c>
       <c r="N211" s="9" t="inlineStr">
         <is>
-          <t>coa.6630.name</t>
+          <t>coa.6620.name</t>
         </is>
       </c>
       <c r="O211" s="10" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="9" t="n">
-        <v>6640</v>
+        <v>6630</v>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Merchant and credit card fees</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
@@ -14850,14 +14852,10 @@
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>AirAg Ops only</t>
-        </is>
-      </c>
-      <c r="I212" s="9" t="inlineStr">
-        <is>
-          <t>Receivables</t>
-        </is>
-      </c>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I212" s="9" t="inlineStr"/>
       <c r="J212" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -14865,33 +14863,33 @@
       </c>
       <c r="K212" s="10" t="inlineStr">
         <is>
-          <t>Bad Debts</t>
+          <t>Bank Charges</t>
         </is>
       </c>
       <c r="L212" s="9" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M212" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
         <is>
-          <t>coa.6640.name</t>
+          <t>coa.6630.name</t>
         </is>
       </c>
       <c r="O212" s="10" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="9" t="n">
-        <v>6700</v>
+        <v>6640</v>
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>Vehicle expenses – administration</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
@@ -14917,10 +14915,14 @@
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I213" s="9" t="inlineStr"/>
+          <t>AirAg Ops only</t>
+        </is>
+      </c>
+      <c r="I213" s="9" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="J213" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -14928,37 +14930,33 @@
       </c>
       <c r="K213" s="10" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Bad Debts</t>
         </is>
       </c>
       <c r="L213" s="9" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="M213" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
         <is>
-          <t>coa.6700.name</t>
-        </is>
-      </c>
-      <c r="O213" s="10" t="inlineStr">
-        <is>
-          <t>GIFI code to confirm with accountant.</t>
-        </is>
-      </c>
+          <t>coa.6640.name</t>
+        </is>
+      </c>
+      <c r="O213" s="10" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="9" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>Travel – administration</t>
+          <t>Vehicle expenses – administration</t>
         </is>
       </c>
       <c r="C214" s="9" t="inlineStr">
@@ -14995,12 +14993,12 @@
       </c>
       <c r="K214" s="10" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="L214" s="9" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="M214" s="9" t="inlineStr">
@@ -15010,18 +15008,22 @@
       </c>
       <c r="N214" s="9" t="inlineStr">
         <is>
-          <t>coa.6800.name</t>
-        </is>
-      </c>
-      <c r="O214" s="10" t="inlineStr"/>
+          <t>coa.6700.name</t>
+        </is>
+      </c>
+      <c r="O214" s="10" t="inlineStr">
+        <is>
+          <t>GIFI code to confirm with accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="9" t="n">
-        <v>6810</v>
+        <v>6800</v>
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
+          <t>Travel – administration</t>
         </is>
       </c>
       <c r="C215" s="9" t="inlineStr">
@@ -15058,12 +15060,12 @@
       </c>
       <c r="K215" s="10" t="inlineStr">
         <is>
-          <t>Entertainment Meals</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="L215" s="9" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="M215" s="9" t="inlineStr">
@@ -15073,22 +15075,18 @@
       </c>
       <c r="N215" s="9" t="inlineStr">
         <is>
-          <t>coa.6810.name</t>
-        </is>
-      </c>
-      <c r="O215" s="10" t="inlineStr">
-        <is>
-          <t>Usually only 50% deductible in Canada and the US; the tax adjustment is made outside the ledger.</t>
-        </is>
-      </c>
+          <t>coa.6800.name</t>
+        </is>
+      </c>
+      <c r="O215" s="10" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="9" t="n">
-        <v>6900</v>
+        <v>6810</v>
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>Amortization – buildings, office and other assets</t>
+          <t>Meals and entertainment</t>
         </is>
       </c>
       <c r="C216" s="9" t="inlineStr">
@@ -15114,14 +15112,10 @@
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
-          <t>System (automatic)</t>
-        </is>
-      </c>
-      <c r="I216" s="9" t="inlineStr">
-        <is>
-          <t>Fixed Assets</t>
-        </is>
-      </c>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I216" s="9" t="inlineStr"/>
       <c r="J216" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -15129,33 +15123,37 @@
       </c>
       <c r="K216" s="10" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Entertainment Meals</t>
         </is>
       </c>
       <c r="L216" s="9" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="M216" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N216" s="9" t="inlineStr">
         <is>
-          <t>coa.6900.name</t>
-        </is>
-      </c>
-      <c r="O216" s="10" t="inlineStr"/>
+          <t>coa.6810.name</t>
+        </is>
+      </c>
+      <c r="O216" s="10" t="inlineStr">
+        <is>
+          <t>Usually only 50% deductible in Canada and the US; the tax adjustment is made outside the ledger.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="9" t="n">
-        <v>6910</v>
+        <v>6900</v>
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>Amortization – intangible assets</t>
+          <t>Amortization – buildings, office and other assets</t>
         </is>
       </c>
       <c r="C217" s="9" t="inlineStr">
@@ -15196,37 +15194,33 @@
       </c>
       <c r="K217" s="10" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="L217" s="9" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="M217" s="9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N217" s="9" t="inlineStr">
         <is>
-          <t>coa.6910.name</t>
-        </is>
-      </c>
-      <c r="O217" s="10" t="inlineStr">
-        <is>
-          <t>GIFI code to confirm with accountant.</t>
-        </is>
-      </c>
+          <t>coa.6900.name</t>
+        </is>
+      </c>
+      <c r="O217" s="10" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="9" t="n">
-        <v>6950</v>
+        <v>6910</v>
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>Small tools and minor equipment</t>
+          <t>Amortization – intangible assets</t>
         </is>
       </c>
       <c r="C218" s="9" t="inlineStr">
@@ -15252,10 +15246,14 @@
       </c>
       <c r="H218" s="9" t="inlineStr">
         <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I218" s="9" t="inlineStr"/>
+          <t>System (automatic)</t>
+        </is>
+      </c>
+      <c r="I218" s="9" t="inlineStr">
+        <is>
+          <t>Fixed Assets</t>
+        </is>
+      </c>
       <c r="J218" s="9" t="inlineStr">
         <is>
           <t>Expenses</t>
@@ -15263,12 +15261,12 @@
       </c>
       <c r="K218" s="10" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="L218" s="9" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="M218" s="9" t="inlineStr">
@@ -15278,18 +15276,22 @@
       </c>
       <c r="N218" s="9" t="inlineStr">
         <is>
-          <t>coa.6950.name</t>
-        </is>
-      </c>
-      <c r="O218" s="10" t="inlineStr"/>
+          <t>coa.6910.name</t>
+        </is>
+      </c>
+      <c r="O218" s="10" t="inlineStr">
+        <is>
+          <t>GIFI code to confirm with accountant.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="9" t="n">
-        <v>6990</v>
+        <v>6950</v>
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>Miscellaneous expenses</t>
+          <t>Small tools and minor equipment</t>
         </is>
       </c>
       <c r="C219" s="9" t="inlineStr">
@@ -15326,131 +15328,131 @@
       </c>
       <c r="K219" s="10" t="inlineStr">
         <is>
+          <t>Supplies &amp; Materials</t>
+        </is>
+      </c>
+      <c r="L219" s="9" t="inlineStr">
+        <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="M219" s="9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N219" s="9" t="inlineStr">
+        <is>
+          <t>coa.6950.name</t>
+        </is>
+      </c>
+      <c r="O219" s="10" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="n">
+        <v>6990</v>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>Miscellaneous expenses</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>Postable</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr"/>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I220" s="9" t="inlineStr"/>
+      <c r="J220" s="9" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="K220" s="10" t="inlineStr">
+        <is>
           <t>Other Miscellaneous Service Cost</t>
         </is>
       </c>
-      <c r="L219" s="9" t="inlineStr">
+      <c r="L220" s="9" t="inlineStr">
         <is>
           <t>9270</t>
         </is>
       </c>
-      <c r="M219" s="9" t="inlineStr">
+      <c r="M220" s="9" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="N219" s="9" t="inlineStr">
+      <c r="N220" s="9" t="inlineStr">
         <is>
           <t>coa.6990.name</t>
         </is>
       </c>
-      <c r="O219" s="10" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="7" t="n">
+      <c r="O220" s="10" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="n">
         <v>7000</v>
       </c>
-      <c r="B220" s="8" t="inlineStr">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>Other income and expenses</t>
         </is>
       </c>
-      <c r="C220" s="7" t="inlineStr">
+      <c r="C221" s="7" t="inlineStr">
         <is>
           <t>Other income / expense</t>
         </is>
       </c>
-      <c r="D220" s="7" t="inlineStr">
+      <c r="D221" s="7" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="E220" s="7" t="inlineStr"/>
-      <c r="F220" s="7" t="inlineStr"/>
-      <c r="G220" s="7" t="inlineStr"/>
-      <c r="H220" s="7" t="inlineStr"/>
-      <c r="I220" s="7" t="inlineStr"/>
-      <c r="J220" s="7" t="inlineStr"/>
-      <c r="K220" s="8" t="inlineStr"/>
-      <c r="L220" s="7" t="inlineStr"/>
-      <c r="M220" s="7" t="inlineStr"/>
-      <c r="N220" s="7" t="inlineStr">
+      <c r="E221" s="7" t="inlineStr"/>
+      <c r="F221" s="7" t="inlineStr"/>
+      <c r="G221" s="7" t="inlineStr"/>
+      <c r="H221" s="7" t="inlineStr"/>
+      <c r="I221" s="7" t="inlineStr"/>
+      <c r="J221" s="7" t="inlineStr"/>
+      <c r="K221" s="8" t="inlineStr"/>
+      <c r="L221" s="7" t="inlineStr"/>
+      <c r="M221" s="7" t="inlineStr"/>
+      <c r="N221" s="7" t="inlineStr">
         <is>
           <t>coa.7000.name</t>
         </is>
       </c>
-      <c r="O220" s="8" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="9" t="n">
-        <v>7010</v>
-      </c>
-      <c r="B221" s="10" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="C221" s="9" t="inlineStr">
-        <is>
-          <t>Other income / expense</t>
-        </is>
-      </c>
-      <c r="D221" s="9" t="inlineStr">
-        <is>
-          <t>Postable</t>
-        </is>
-      </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F221" s="9" t="inlineStr"/>
-      <c r="G221" s="9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H221" s="9" t="inlineStr">
-        <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I221" s="9" t="inlineStr"/>
-      <c r="J221" s="9" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-      <c r="K221" s="10" t="inlineStr">
-        <is>
-          <t>Interest Earned</t>
-        </is>
-      </c>
-      <c r="L221" s="9" t="inlineStr">
-        <is>
-          <t>8090</t>
-        </is>
-      </c>
-      <c r="M221" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N221" s="9" t="inlineStr">
-        <is>
-          <t>coa.7010.name</t>
-        </is>
-      </c>
-      <c r="O221" s="10" t="inlineStr"/>
+      <c r="O221" s="8" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="9" t="n">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>Foreign exchange gains and losses</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="C222" s="9" t="inlineStr">
@@ -15465,7 +15467,7 @@
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>Credit / Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr"/>
@@ -15487,37 +15489,33 @@
       </c>
       <c r="K222" s="10" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Income</t>
+          <t>Interest Earned</t>
         </is>
       </c>
       <c r="L222" s="9" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="M222" s="9" t="inlineStr">
         <is>
-          <t>10 / 26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N222" s="9" t="inlineStr">
         <is>
-          <t>coa.7020.name</t>
-        </is>
-      </c>
-      <c r="O222" s="10" t="inlineStr">
-        <is>
-          <t>CAD/USD revaluation of bank, receivable and payable balances.</t>
-        </is>
-      </c>
+          <t>coa.7010.name</t>
+        </is>
+      </c>
+      <c r="O222" s="10" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="9" t="n">
-        <v>7030</v>
+        <v>7020</v>
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>Gain or loss on disposal of assets</t>
+          <t>Foreign exchange gains and losses</t>
         </is>
       </c>
       <c r="C223" s="9" t="inlineStr">
@@ -15546,11 +15544,7 @@
           <t>Manual or AirAg Ops</t>
         </is>
       </c>
-      <c r="I223" s="9" t="inlineStr">
-        <is>
-          <t>Fixed Assets</t>
-        </is>
-      </c>
+      <c r="I223" s="9" t="inlineStr"/>
       <c r="J223" s="9" t="inlineStr">
         <is>
           <t>Other Income</t>
@@ -15558,33 +15552,37 @@
       </c>
       <c r="K223" s="10" t="inlineStr">
         <is>
-          <t>Gain/Loss on Sale of Fixed Assets</t>
+          <t>Other Miscellaneous Income</t>
         </is>
       </c>
       <c r="L223" s="9" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="M223" s="9" t="inlineStr">
         <is>
-          <t>9 (Form 4797)</t>
+          <t>10 / 26</t>
         </is>
       </c>
       <c r="N223" s="9" t="inlineStr">
         <is>
-          <t>coa.7030.name</t>
-        </is>
-      </c>
-      <c r="O223" s="10" t="inlineStr"/>
+          <t>coa.7020.name</t>
+        </is>
+      </c>
+      <c r="O223" s="10" t="inlineStr">
+        <is>
+          <t>CAD/USD revaluation of bank, receivable and payable balances.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="9" t="n">
-        <v>7040</v>
+        <v>7030</v>
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>Government grants and subsidies</t>
+          <t>Gain or loss on disposal of assets</t>
         </is>
       </c>
       <c r="C224" s="9" t="inlineStr">
@@ -15599,7 +15597,7 @@
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Credit / Debit</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr"/>
@@ -15613,7 +15611,11 @@
           <t>Manual or AirAg Ops</t>
         </is>
       </c>
-      <c r="I224" s="9" t="inlineStr"/>
+      <c r="I224" s="9" t="inlineStr">
+        <is>
+          <t>Fixed Assets</t>
+        </is>
+      </c>
       <c r="J224" s="9" t="inlineStr">
         <is>
           <t>Other Income</t>
@@ -15621,37 +15623,33 @@
       </c>
       <c r="K224" s="10" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Income</t>
+          <t>Gain/Loss on Sale of Fixed Assets</t>
         </is>
       </c>
       <c r="L224" s="9" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="M224" s="9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9 (Form 4797)</t>
         </is>
       </c>
       <c r="N224" s="9" t="inlineStr">
         <is>
-          <t>coa.7040.name</t>
-        </is>
-      </c>
-      <c r="O224" s="10" t="inlineStr">
-        <is>
-          <t>Non-repayable contributions, e.g. RTRI.</t>
-        </is>
-      </c>
+          <t>coa.7030.name</t>
+        </is>
+      </c>
+      <c r="O224" s="10" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="9" t="n">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>Fuel tax credits and refunds</t>
+          <t>Government grants and subsidies</t>
         </is>
       </c>
       <c r="C225" s="9" t="inlineStr">
@@ -15680,11 +15678,7 @@
           <t>Manual or AirAg Ops</t>
         </is>
       </c>
-      <c r="I225" s="9" t="inlineStr">
-        <is>
-          <t>Fuel</t>
-        </is>
-      </c>
+      <c r="I225" s="9" t="inlineStr"/>
       <c r="J225" s="9" t="inlineStr">
         <is>
           <t>Other Income</t>
@@ -15707,22 +15701,22 @@
       </c>
       <c r="N225" s="9" t="inlineStr">
         <is>
-          <t>coa.7050.name</t>
+          <t>coa.7040.name</t>
         </is>
       </c>
       <c r="O225" s="10" t="inlineStr">
         <is>
-          <t>US: the Form 4136 credit is included in income.</t>
+          <t>Non-repayable contributions, e.g. RTRI.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="9" t="n">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>Insurance proceeds and recoveries</t>
+          <t>Fuel tax credits and refunds</t>
         </is>
       </c>
       <c r="C226" s="9" t="inlineStr">
@@ -15751,7 +15745,11 @@
           <t>Manual or AirAg Ops</t>
         </is>
       </c>
-      <c r="I226" s="9" t="inlineStr"/>
+      <c r="I226" s="9" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
       <c r="J226" s="9" t="inlineStr">
         <is>
           <t>Other Income</t>
@@ -15774,18 +15772,22 @@
       </c>
       <c r="N226" s="9" t="inlineStr">
         <is>
-          <t>coa.7060.name</t>
-        </is>
-      </c>
-      <c r="O226" s="10" t="inlineStr"/>
+          <t>coa.7050.name</t>
+        </is>
+      </c>
+      <c r="O226" s="10" t="inlineStr">
+        <is>
+          <t>US: the Form 4136 credit is included in income.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="9" t="n">
-        <v>7100</v>
+        <v>7060</v>
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>Interest – aircraft and equipment loans</t>
+          <t>Insurance proceeds and recoveries</t>
         </is>
       </c>
       <c r="C227" s="9" t="inlineStr">
@@ -15800,7 +15802,7 @@
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr"/>
@@ -15817,38 +15819,38 @@
       <c r="I227" s="9" t="inlineStr"/>
       <c r="J227" s="9" t="inlineStr">
         <is>
-          <t>Other Expense</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="K227" s="10" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Expense</t>
+          <t>Other Miscellaneous Income</t>
         </is>
       </c>
       <c r="L227" s="9" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="M227" s="9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N227" s="9" t="inlineStr">
         <is>
-          <t>coa.7100.name</t>
+          <t>coa.7060.name</t>
         </is>
       </c>
       <c r="O227" s="10" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="9" t="n">
-        <v>7110</v>
+        <v>7100</v>
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>Interest – operating line and other</t>
+          <t>Interest – aircraft and equipment loans</t>
         </is>
       </c>
       <c r="C228" s="9" t="inlineStr">
@@ -15890,7 +15892,7 @@
       </c>
       <c r="L228" s="9" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="M228" s="9" t="inlineStr">
@@ -15900,18 +15902,18 @@
       </c>
       <c r="N228" s="9" t="inlineStr">
         <is>
-          <t>coa.7110.name</t>
+          <t>coa.7100.name</t>
         </is>
       </c>
       <c r="O228" s="10" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="9" t="n">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>Interest on lease liabilities</t>
+          <t>Interest – operating line and other</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
@@ -15963,18 +15965,18 @@
       </c>
       <c r="N229" s="9" t="inlineStr">
         <is>
-          <t>coa.7120.name</t>
+          <t>coa.7110.name</t>
         </is>
       </c>
       <c r="O229" s="10" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="9" t="n">
-        <v>7200</v>
+        <v>7120</v>
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>Penalties, fines and non-deductible expenses</t>
+          <t>Interest on lease liabilities</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
@@ -16011,131 +16013,131 @@
       </c>
       <c r="K230" s="10" t="inlineStr">
         <is>
+          <t>Other Miscellaneous Expense</t>
+        </is>
+      </c>
+      <c r="L230" s="9" t="inlineStr">
+        <is>
+          <t>8710</t>
+        </is>
+      </c>
+      <c r="M230" s="9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N230" s="9" t="inlineStr">
+        <is>
+          <t>coa.7120.name</t>
+        </is>
+      </c>
+      <c r="O230" s="10" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="9" t="n">
+        <v>7200</v>
+      </c>
+      <c r="B231" s="10" t="inlineStr">
+        <is>
+          <t>Penalties, fines and non-deductible expenses</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="inlineStr">
+        <is>
+          <t>Other income / expense</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>Postable</t>
+        </is>
+      </c>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr"/>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I231" s="9" t="inlineStr"/>
+      <c r="J231" s="9" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="K231" s="10" t="inlineStr">
+        <is>
           <t>Penalties &amp; Settlements</t>
         </is>
       </c>
-      <c r="L230" s="9" t="inlineStr">
+      <c r="L231" s="9" t="inlineStr">
         <is>
           <t>9270</t>
         </is>
       </c>
-      <c r="M230" s="9" t="inlineStr">
+      <c r="M231" s="9" t="inlineStr">
         <is>
           <t>— (not deductible)</t>
         </is>
       </c>
-      <c r="N230" s="9" t="inlineStr">
+      <c r="N231" s="9" t="inlineStr">
         <is>
           <t>coa.7200.name</t>
         </is>
       </c>
-      <c r="O230" s="10" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="7" t="n">
+      <c r="O231" s="10" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="n">
         <v>8000</v>
       </c>
-      <c r="B231" s="8" t="inlineStr">
+      <c r="B232" s="8" t="inlineStr">
         <is>
           <t>Income taxes</t>
         </is>
       </c>
-      <c r="C231" s="7" t="inlineStr">
+      <c r="C232" s="7" t="inlineStr">
         <is>
           <t>Income tax</t>
         </is>
       </c>
-      <c r="D231" s="7" t="inlineStr">
+      <c r="D232" s="7" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="E231" s="7" t="inlineStr"/>
-      <c r="F231" s="7" t="inlineStr"/>
-      <c r="G231" s="7" t="inlineStr"/>
-      <c r="H231" s="7" t="inlineStr"/>
-      <c r="I231" s="7" t="inlineStr"/>
-      <c r="J231" s="7" t="inlineStr"/>
-      <c r="K231" s="8" t="inlineStr"/>
-      <c r="L231" s="7" t="inlineStr"/>
-      <c r="M231" s="7" t="inlineStr"/>
-      <c r="N231" s="7" t="inlineStr">
+      <c r="E232" s="7" t="inlineStr"/>
+      <c r="F232" s="7" t="inlineStr"/>
+      <c r="G232" s="7" t="inlineStr"/>
+      <c r="H232" s="7" t="inlineStr"/>
+      <c r="I232" s="7" t="inlineStr"/>
+      <c r="J232" s="7" t="inlineStr"/>
+      <c r="K232" s="8" t="inlineStr"/>
+      <c r="L232" s="7" t="inlineStr"/>
+      <c r="M232" s="7" t="inlineStr"/>
+      <c r="N232" s="7" t="inlineStr">
         <is>
           <t>coa.8000.name</t>
         </is>
       </c>
-      <c r="O231" s="8" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="9" t="n">
-        <v>8010</v>
-      </c>
-      <c r="B232" s="10" t="inlineStr">
-        <is>
-          <t>Current income taxes</t>
-        </is>
-      </c>
-      <c r="C232" s="9" t="inlineStr">
-        <is>
-          <t>Income tax</t>
-        </is>
-      </c>
-      <c r="D232" s="9" t="inlineStr">
-        <is>
-          <t>Postable</t>
-        </is>
-      </c>
-      <c r="E232" s="9" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F232" s="9" t="inlineStr"/>
-      <c r="G232" s="9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H232" s="9" t="inlineStr">
-        <is>
-          <t>Manual or AirAg Ops</t>
-        </is>
-      </c>
-      <c r="I232" s="9" t="inlineStr"/>
-      <c r="J232" s="9" t="inlineStr">
-        <is>
-          <t>Other Expense</t>
-        </is>
-      </c>
-      <c r="K232" s="10" t="inlineStr">
-        <is>
-          <t>Other Miscellaneous Expense</t>
-        </is>
-      </c>
-      <c r="L232" s="9" t="inlineStr">
-        <is>
-          <t>9990</t>
-        </is>
-      </c>
-      <c r="M232" s="9" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N232" s="9" t="inlineStr">
-        <is>
-          <t>coa.8010.name</t>
-        </is>
-      </c>
-      <c r="O232" s="10" t="inlineStr"/>
+      <c r="O232" s="8" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="9" t="n">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>Deferred income taxes</t>
+          <t>Current income taxes</t>
         </is>
       </c>
       <c r="C233" s="9" t="inlineStr">
@@ -16177,20 +16179,83 @@
       </c>
       <c r="L233" s="9" t="inlineStr">
         <is>
+          <t>9990</t>
+        </is>
+      </c>
+      <c r="M233" s="9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N233" s="9" t="inlineStr">
+        <is>
+          <t>coa.8010.name</t>
+        </is>
+      </c>
+      <c r="O233" s="10" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="n">
+        <v>8020</v>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>Deferred income taxes</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>Postable</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr"/>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>Manual or AirAg Ops</t>
+        </is>
+      </c>
+      <c r="I234" s="9" t="inlineStr"/>
+      <c r="J234" s="9" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="K234" s="10" t="inlineStr">
+        <is>
+          <t>Other Miscellaneous Expense</t>
+        </is>
+      </c>
+      <c r="L234" s="9" t="inlineStr">
+        <is>
           <t>9995</t>
         </is>
       </c>
-      <c r="M233" s="9" t="inlineStr">
+      <c r="M234" s="9" t="inlineStr">
         <is>
           <t>— (book only)</t>
         </is>
       </c>
-      <c r="N233" s="9" t="inlineStr">
+      <c r="N234" s="9" t="inlineStr">
         <is>
           <t>coa.8020.name</t>
         </is>
       </c>
-      <c r="O233" s="10" t="inlineStr"/>
+      <c r="O234" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O233"/>
@@ -16204,7 +16269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20598,2623 +20663,2653 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="n">
+      <c r="A147" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>coa.4800.name</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Miscellaneous and other income</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Revenus divers et autres produits</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ingresos varios y otros ingresos</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Receitas diversas e outras receitas</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
         <v>4900</v>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>coa.4900.name</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>Sales discounts, rebates and allowances</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>Escomptes, remises et rabais sur ventes</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>Descuentos, bonificaciones y rebajas sobre ventas</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>Descontos, bonificações e abatimentos sobre vendas</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="11" t="n">
+    <row r="149">
+      <c r="A149" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="B148" s="11" t="inlineStr">
+      <c r="B149" s="11" t="inlineStr">
         <is>
           <t>coa.5000.name</t>
         </is>
       </c>
-      <c r="C148" s="11" t="inlineStr">
+      <c r="C149" s="11" t="inlineStr">
         <is>
           <t>Direct costs – flight operations</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Coûts directs – opérations aériennes</t>
         </is>
       </c>
-      <c r="E148" s="11" t="inlineStr">
+      <c r="E149" s="11" t="inlineStr">
         <is>
           <t>Costos directos – operaciones de vuelo</t>
         </is>
       </c>
-      <c r="F148" s="11" t="inlineStr">
+      <c r="F149" s="11" t="inlineStr">
         <is>
           <t>Custos diretos – operações aéreas</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="4" t="n">
-        <v>5010</v>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>coa.5010.name</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>Chemical cost of sales (company-owned)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>Coût des produits chimiques vendus (propriété de l’entreprise)</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>Costo de agroquímicos vendidos (propios)</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>Custo dos defensivos vendidos (próprios)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>coa.5020.name</t>
+          <t>coa.5010.name</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Fertilizer and seed cost of sales</t>
+          <t>Chemical cost of sales (company-owned)</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Coût des engrais et semences vendus</t>
+          <t>Coût des produits chimiques vendus (propriété de l’entreprise)</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Costo de fertilizantes y semillas vendidos</t>
+          <t>Costo de agroquímicos vendidos (propios)</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Custo de fertilizantes e sementes vendidos</t>
+          <t>Custo dos defensivos vendidos (próprios)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>coa.5030.name</t>
+          <t>coa.5020.name</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Supplier rebates and early-order discounts</t>
+          <t>Fertilizer and seed cost of sales</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Remises fournisseurs et escomptes de précommande</t>
+          <t>Coût des engrais et semences vendus</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Bonificaciones de proveedores y descuentos de preventa</t>
+          <t>Costo de fertilizantes y semillas vendidos</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Bonificações de fornecedores e descontos de pré-venda</t>
+          <t>Custo de fertilizantes e sementes vendidos</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
-        <v>5100</v>
+        <v>5030</v>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>coa.5100.name</t>
+          <t>coa.5030.name</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Aviation fuel and oil</t>
+          <t>Supplier rebates and early-order discounts</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Carburant et huile d’aviation</t>
+          <t>Remises fournisseurs et escomptes de précommande</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Combustible y aceite de aviación</t>
+          <t>Bonificaciones de proveedores y descuentos de preventa</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Combustível e óleo de aviação</t>
+          <t>Bonificações de fornecedores e descontos de pré-venda</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>coa.5200.name</t>
+          <t>coa.5100.name</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Pilot wages</t>
+          <t>Aviation fuel and oil</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Salaires des pilotes</t>
+          <t>Carburant et huile d’aviation</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Sueldos de pilotos</t>
+          <t>Combustible y aceite de aviación</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Salários de pilotos</t>
+          <t>Combustível e óleo de aviação</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
-        <v>5210</v>
+        <v>5200</v>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>coa.5210.name</t>
+          <t>coa.5200.name</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Loader and ground crew wages</t>
+          <t>Pilot wages</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Salaires des chargeurs et du personnel au sol</t>
+          <t>Salaires des pilotes</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Sueldos de cargadores y personal de tierra</t>
+          <t>Sueldos de pilotos</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Salários de carregadores e equipe de solo</t>
+          <t>Salários de pilotos</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
-        <v>5220</v>
+        <v>5210</v>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>coa.5220.name</t>
+          <t>coa.5210.name</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Maintenance labour – AMEs and mechanics</t>
+          <t>Loader and ground crew wages</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Main-d’œuvre d’entretien – TEA et mécaniciens</t>
+          <t>Salaires des chargeurs et du personnel au sol</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Mano de obra de mantenimiento – técnicos y mecánicos</t>
+          <t>Sueldos de cargadores y personal de tierra</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Mão de obra de manutenção – técnicos e mecânicos</t>
+          <t>Salários de carregadores e equipe de solo</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
-        <v>5250</v>
+        <v>5220</v>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>coa.5250.name</t>
+          <t>coa.5220.name</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Direct payroll burden – CPP/QPP and EI/QPIP</t>
+          <t>Maintenance labour – AMEs and mechanics</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales directes – RPC/RRQ et AE/RQAP</t>
+          <t>Main-d’œuvre d’entretien – TEA et mécaniciens</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales directas – CPP/QPP y EI/QPIP</t>
+          <t>Mano de obra de mantenimiento – técnicos y mecánicos</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Encargos diretos – CPP/QPP e EI/QPIP</t>
+          <t>Mão de obra de manutenção – técnicos e mecânicos</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
-        <v>5255</v>
+        <v>5250</v>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>coa.5255.name</t>
+          <t>coa.5250.name</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Direct payroll burden – FICA, FUTA and SUTA</t>
+          <t>Direct payroll burden – CPP/QPP and EI/QPIP</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales directes – FICA, FUTA et SUTA</t>
+          <t>Charges sociales directes – RPC/RRQ et AE/RQAP</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales directas – FICA, FUTA y SUTA</t>
+          <t>Cargas sociales directas – CPP/QPP y EI/QPIP</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Encargos diretos – FICA, FUTA e SUTA</t>
+          <t>Encargos diretos – CPP/QPP e EI/QPIP</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
-        <v>5260</v>
+        <v>5255</v>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>coa.5260.name</t>
+          <t>coa.5255.name</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Direct payroll burden – employer health tax and workers’ compensation</t>
+          <t>Direct payroll burden – FICA, FUTA and SUTA</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales directes – impôt-santé et indemnisation des accidentés</t>
+          <t>Charges sociales directes – FICA, FUTA et SUTA</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales directas – impuesto de salud y riesgos laborales</t>
+          <t>Cargas sociales directas – FICA, FUTA y SUTA</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Encargos diretos – imposto de saúde e seguro de acidentes</t>
+          <t>Encargos diretos – FICA, FUTA e SUTA</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
-        <v>5265</v>
+        <v>5260</v>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>coa.5265.name</t>
+          <t>coa.5260.name</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Direct payroll burden – benefits and retirement contributions</t>
+          <t>Direct payroll burden – employer health tax and workers’ compensation</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales directes – avantages sociaux et cotisations de retraite</t>
+          <t>Charges sociales directes – impôt-santé et indemnisation des accidentés</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales directas – beneficios y aportes jubilatorios</t>
+          <t>Cargas sociales directas – impuesto de salud y riesgos laborales</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Encargos diretos – benefícios e contribuições previdenciárias</t>
+          <t>Encargos diretos – imposto de saúde e seguro de acidentes</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
-        <v>5270</v>
+        <v>5265</v>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>coa.5270.name</t>
+          <t>coa.5265.name</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Direct payroll – vacation and statutory holiday pay</t>
+          <t>Direct payroll burden – benefits and retirement contributions</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Paie directe – vacances et jours fériés</t>
+          <t>Charges sociales directes – avantages sociaux et cotisations de retraite</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Nómina directa – vacaciones y feriados</t>
+          <t>Cargas sociales directas – beneficios y aportes jubilatorios</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Folha direta – férias e feriados</t>
+          <t>Encargos diretos – benefícios e contribuições previdenciárias</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
-        <v>5300</v>
+        <v>5270</v>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>coa.5300.name</t>
+          <t>coa.5270.name</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – parts issued</t>
+          <t>Direct payroll – vacation and statutory holiday pay</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Entretien des aéronefs – pièces utilisées</t>
+          <t>Paie directe – vacances et jours fériés</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de aeronaves – repuestos utilizados</t>
+          <t>Nómina directa – vacaciones y feriados</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de aeronaves – peças aplicadas</t>
+          <t>Folha direta – férias e feriados</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
-        <v>5310</v>
+        <v>5300</v>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>coa.5310.name</t>
+          <t>coa.5300.name</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – outside services</t>
+          <t>Aircraft maintenance – parts issued</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Entretien des aéronefs – services externes</t>
+          <t>Entretien des aéronefs – pièces utilisées</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de aeronaves – servicios externos</t>
+          <t>Mantenimiento de aeronaves – repuestos utilizados</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de aeronaves – serviços de terceiros</t>
+          <t>Manutenção de aeronaves – peças aplicadas</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
-        <v>5320</v>
+        <v>5310</v>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>coa.5320.name</t>
+          <t>coa.5310.name</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – engine and propeller overhauls (expensed)</t>
+          <t>Aircraft maintenance – outside services</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Entretien des aéronefs – révisions moteurs et hélices (passées en charges)</t>
+          <t>Entretien des aéronefs – services externes</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de aeronaves – overhaul de motores y hélices (gasto)</t>
+          <t>Mantenimiento de aeronaves – servicios externos</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de aeronaves – revisões de motores e hélices (despesa)</t>
+          <t>Manutenção de aeronaves – serviços de terceiros</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
-        <v>5330</v>
+        <v>5320</v>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>coa.5330.name</t>
+          <t>coa.5320.name</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – components, avionics and dispersal systems</t>
+          <t>Aircraft maintenance – engine and propeller overhauls (expensed)</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Entretien des aéronefs – composants, avionique et systèmes d’épandage</t>
+          <t>Entretien des aéronefs – révisions moteurs et hélices (passées en charges)</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de aeronaves – componentes, aviónica y sistemas de aplicación</t>
+          <t>Mantenimiento de aeronaves – overhaul de motores y hélices (gasto)</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de aeronaves – componentes, aviônicos e sistemas de aplicação</t>
+          <t>Manutenção de aeronaves – revisões de motores e hélices (despesa)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
-        <v>5340</v>
+        <v>5330</v>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>coa.5340.name</t>
+          <t>coa.5330.name</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – shop consumables</t>
+          <t>Aircraft maintenance – components, avionics and dispersal systems</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Entretien des aéronefs – fournitures d’atelier</t>
+          <t>Entretien des aéronefs – composants, avionique et systèmes d’épandage</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de aeronaves – consumibles de taller</t>
+          <t>Mantenimiento de aeronaves – componentes, aviónica y sistemas de aplicación</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de aeronaves – consumíveis de oficina</t>
+          <t>Manutenção de aeronaves – componentes, aviônicos e sistemas de aplicação</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>coa.5400.name</t>
+          <t>coa.5340.name</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Aircraft hull insurance</t>
+          <t>Aircraft maintenance – shop consumables</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Assurance corps d’aéronefs</t>
+          <t>Entretien des aéronefs – fournitures d’atelier</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Seguro de casco de aeronaves</t>
+          <t>Mantenimiento de aeronaves – consumibles de taller</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>Seguro de casco de aeronaves</t>
+          <t>Manutenção de aeronaves – consumíveis de oficina</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
-        <v>5410</v>
+        <v>5400</v>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>coa.5410.name</t>
+          <t>coa.5400.name</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Aviation and aerial application liability insurance</t>
+          <t>Aircraft hull insurance</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Assurance responsabilité aviation et application aérienne</t>
+          <t>Assurance corps d’aéronefs</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Seguro de responsabilidad de aviación y aplicación aérea</t>
+          <t>Seguro de casco de aeronaves</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Seguro de responsabilidade aeronáutica e de aplicação aérea</t>
+          <t>Seguro de casco de aeronaves</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
-        <v>5500</v>
+        <v>5410</v>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>coa.5500.name</t>
+          <t>coa.5410.name</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Aircraft leases and rentals</t>
+          <t>Aviation and aerial application liability insurance</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Location d’aéronefs</t>
+          <t>Assurance responsabilité aviation et application aérienne</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Arrendamiento y alquiler de aeronaves</t>
+          <t>Seguro de responsabilidad de aviación y aplicación aérea</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Arrendamento e aluguel de aeronaves</t>
+          <t>Seguro de responsabilidade aeronáutica e de aplicação aérea</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
-        <v>5510</v>
+        <v>5500</v>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>coa.5510.name</t>
+          <t>coa.5500.name</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Hangar, tie-down and landing fees</t>
+          <t>Aircraft leases and rentals</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Frais de hangar, d’amarrage et d’atterrissage</t>
+          <t>Location d’aéronefs</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Tarifas de hangar, amarre y aterrizaje</t>
+          <t>Arrendamiento y alquiler de aeronaves</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Taxas de hangar, amarração e pouso</t>
+          <t>Arrendamento e aluguel de aeronaves</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
-        <v>5600</v>
+        <v>5510</v>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>coa.5600.name</t>
+          <t>coa.5510.name</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GPS, guidance and flight-tracking subscriptions</t>
+          <t>Hangar, tie-down and landing fees</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Abonnements GPS, guidage et suivi de vol</t>
+          <t>Frais de hangar, d’amarrage et d’atterrissage</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Suscripciones de GPS, guiado y seguimiento de vuelos</t>
+          <t>Tarifas de hangar, amarre y aterrizaje</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>Assinaturas de GPS, navegação e rastreamento de voo</t>
+          <t>Taxas de hangar, amarração e pouso</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
-        <v>5610</v>
+        <v>5600</v>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>coa.5610.name</t>
+          <t>coa.5600.name</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Crew travel, lodging and per diem</t>
+          <t>GPS, guidance and flight-tracking subscriptions</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Déplacements, hébergement et indemnités journalières des équipages</t>
+          <t>Abonnements GPS, guidage et suivi de vol</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Viajes, alojamiento y viáticos de tripulación</t>
+          <t>Suscripciones de GPS, guiado y seguimiento de vuelos</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Viagens, hospedagem e diárias da equipe</t>
+          <t>Assinaturas de GPS, navegação e rastreamento de voo</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
-        <v>5620</v>
+        <v>5610</v>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>coa.5620.name</t>
+          <t>coa.5610.name</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Ground support vehicle fuel</t>
+          <t>Crew travel, lodging and per diem</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Carburant des véhicules de soutien au sol</t>
+          <t>Déplacements, hébergement et indemnités journalières des équipages</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Combustible de vehículos de apoyo en tierra</t>
+          <t>Viajes, alojamiento y viáticos de tripulación</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>Combustível de veículos de apoio em solo</t>
+          <t>Viagens, hospedagem e diárias da equipe</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>coa.5630.name</t>
+          <t>coa.5620.name</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Vehicle and equipment maintenance – parts issued</t>
+          <t>Ground support vehicle fuel</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Entretien des véhicules et de l’équipement – pièces utilisées</t>
+          <t>Carburant des véhicules de soutien au sol</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de vehículos y equipos – repuestos utilizados</t>
+          <t>Combustible de vehículos de apoyo en tierra</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de veículos e equipamentos – peças aplicadas</t>
+          <t>Combustível de veículos de apoio em solo</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
-        <v>5640</v>
+        <v>5630</v>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>coa.5640.name</t>
+          <t>coa.5630.name</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Vehicle and equipment maintenance – outside services</t>
+          <t>Vehicle and equipment maintenance – parts issued</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Entretien des véhicules et de l’équipement – services externes</t>
+          <t>Entretien des véhicules et de l’équipement – pièces utilisées</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Mantenimiento de vehículos y equipos – servicios externos</t>
+          <t>Mantenimiento de vehículos y equipos – repuestos utilizados</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>Manutenção de veículos e equipamentos – serviços de terceiros</t>
+          <t>Manutenção de veículos e equipamentos – peças aplicadas</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
-        <v>5650</v>
+        <v>5640</v>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>coa.5650.name</t>
+          <t>coa.5640.name</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Equipment and vehicle rentals</t>
+          <t>Vehicle and equipment maintenance – outside services</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Location d’équipement et de véhicules</t>
+          <t>Entretien des véhicules et de l’équipement – services externes</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Alquiler de equipos y vehículos</t>
+          <t>Mantenimiento de vehículos y equipos – servicios externos</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Aluguel de equipamentos e veículos</t>
+          <t>Manutenção de veículos e equipamentos – serviços de terceiros</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
-        <v>5700</v>
+        <v>5650</v>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>coa.5700.name</t>
+          <t>coa.5650.name</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Subcontracted aerial application</t>
+          <t>Equipment and vehicle rentals</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Application aérienne en sous-traitance</t>
+          <t>Location d’équipement et de véhicules</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Aplicación aérea subcontratada</t>
+          <t>Alquiler de equipos y vehículos</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>Aplicação aérea terceirizada</t>
+          <t>Aluguel de equipamentos e veículos</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
-        <v>5710</v>
+        <v>5700</v>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>coa.5710.name</t>
+          <t>coa.5700.name</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Containment, rinsate and disposal costs</t>
+          <t>Subcontracted aerial application</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Coûts de confinement, d’eau de rinçage et d’élimination</t>
+          <t>Application aérienne en sous-traitance</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Costos de contención, agua de enjuague y disposición</t>
+          <t>Aplicación aérea subcontratada</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Custos de contenção, água de enxágue e descarte</t>
+          <t>Aplicação aérea terceirizada</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
-        <v>5800</v>
+        <v>5710</v>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>coa.5800.name</t>
+          <t>coa.5710.name</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Amortization – aircraft</t>
+          <t>Containment, rinsate and disposal costs</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Amortissement – aéronefs</t>
+          <t>Coûts de confinement, d’eau de rinçage et d’élimination</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Depreciación – aeronaves</t>
+          <t>Costos de contención, agua de enjuague y disposición</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>Depreciação – aeronaves</t>
+          <t>Custos de contenção, água de enxágue e descarte</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
-        <v>5810</v>
+        <v>5800</v>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>coa.5810.name</t>
+          <t>coa.5800.name</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Amortization – vehicles and ground equipment</t>
+          <t>Amortization – aircraft</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Amortissement – véhicules et équipement au sol</t>
+          <t>Amortissement – aéronefs</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Depreciación – vehículos y equipos de tierra</t>
+          <t>Depreciación – aeronaves</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Depreciação – veículos e equipamentos de solo</t>
+          <t>Depreciação – aeronaves</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
-        <v>5900</v>
+        <v>5810</v>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>coa.5900.name</t>
+          <t>coa.5810.name</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Inventory adjustments – parts</t>
+          <t>Amortization – vehicles and ground equipment</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Ajustements de stocks – pièces</t>
+          <t>Amortissement – véhicules et équipement au sol</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Ajustes de inventario – repuestos</t>
+          <t>Depreciación – vehículos y equipos de tierra</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>Ajustes de estoque – peças</t>
+          <t>Depreciação – veículos e equipamentos de solo</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
-        <v>5910</v>
+        <v>5900</v>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>coa.5910.name</t>
+          <t>coa.5900.name</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Inventory adjustments – chemicals and fuel</t>
+          <t>Inventory adjustments – parts</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Ajustements de stocks – produits chimiques et carburant</t>
+          <t>Ajustements de stocks – pièces</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Ajustes de inventario – agroquímicos y combustible</t>
+          <t>Ajustes de inventario – repuestos</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Ajustes de estoque – defensivos e combustível</t>
+          <t>Ajustes de estoque – peças</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n">
+        <v>5910</v>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>coa.5910.name</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Inventory adjustments – chemicals and fuel</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Ajustements de stocks – produits chimiques et carburant</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Ajustes de inventario – agroquímicos y combustible</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Ajustes de estoque – defensivos e combustível</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
         <v>5920</v>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B183" s="4" t="inlineStr">
         <is>
           <t>coa.5920.name</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C183" s="4" t="inlineStr">
         <is>
           <t>Freight-in, customs and duty</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D183" s="4" t="inlineStr">
         <is>
           <t>Transport à l’achat, douanes et droits</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
+      <c r="E183" s="4" t="inlineStr">
         <is>
           <t>Fletes de compra, aduanas y aranceles</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="F183" s="4" t="inlineStr">
         <is>
           <t>Fretes de compra, alfândega e impostos de importação</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="11" t="n">
+    <row r="184">
+      <c r="A184" s="11" t="n">
         <v>6000</v>
       </c>
-      <c r="B183" s="11" t="inlineStr">
+      <c r="B184" s="11" t="inlineStr">
         <is>
           <t>coa.6000.name</t>
         </is>
       </c>
-      <c r="C183" s="11" t="inlineStr">
+      <c r="C184" s="11" t="inlineStr">
         <is>
           <t>Operating and administrative expenses</t>
         </is>
       </c>
-      <c r="D183" s="11" t="inlineStr">
+      <c r="D184" s="11" t="inlineStr">
         <is>
           <t>Charges d’exploitation et d’administration</t>
         </is>
       </c>
-      <c r="E183" s="11" t="inlineStr">
+      <c r="E184" s="11" t="inlineStr">
         <is>
           <t>Gastos operativos y administrativos</t>
         </is>
       </c>
-      <c r="F183" s="11" t="inlineStr">
+      <c r="F184" s="11" t="inlineStr">
         <is>
           <t>Despesas operacionais e administrativas</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="n">
-        <v>6010</v>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>coa.6010.name</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>Publicité et promotion</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>Publicidad y promoción</t>
-        </is>
-      </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>Publicidade e promoção</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>coa.6020.name</t>
+          <t>coa.6010.name</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Trade shows and association events</t>
+          <t>Advertising and promotion</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Salons professionnels et événements d’associations</t>
+          <t>Publicité et promotion</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Ferias comerciales y eventos de asociaciones</t>
+          <t>Publicidad y promoción</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Feiras e eventos de associações</t>
+          <t>Publicidade e promoção</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n">
-        <v>6100</v>
+        <v>6020</v>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>coa.6100.name</t>
+          <t>coa.6020.name</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Salaries – management</t>
+          <t>Trade shows and association events</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Salaires – direction</t>
+          <t>Salons professionnels et événements d’associations</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Sueldos – gerencia</t>
+          <t>Ferias comerciales y eventos de asociaciones</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>Salários – gerência</t>
+          <t>Feiras e eventos de associações</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
-        <v>6110</v>
+        <v>6100</v>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>coa.6110.name</t>
+          <t>coa.6100.name</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Salaries – office and dispatch staff</t>
+          <t>Salaries – management</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Salaires – personnel de bureau et de répartition</t>
+          <t>Salaires – direction</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Sueldos – personal de oficina y despacho</t>
+          <t>Sueldos – gerencia</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Salários – equipe de escritório e despacho</t>
+          <t>Salários – gerência</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
-        <v>6150</v>
+        <v>6110</v>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>coa.6150.name</t>
+          <t>coa.6110.name</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Payroll burden – CPP/QPP and EI/QPIP</t>
+          <t>Salaries – office and dispatch staff</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales – RPC/RRQ et AE/RQAP</t>
+          <t>Salaires – personnel de bureau et de répartition</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales – CPP/QPP y EI/QPIP</t>
+          <t>Sueldos – personal de oficina y despacho</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>Encargos – CPP/QPP e EI/QPIP</t>
+          <t>Salários – equipe de escritório e despacho</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
-        <v>6155</v>
+        <v>6150</v>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>coa.6155.name</t>
+          <t>coa.6150.name</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Payroll burden – FICA, FUTA and SUTA</t>
+          <t>Payroll burden – CPP/QPP and EI/QPIP</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales – FICA, FUTA et SUTA</t>
+          <t>Charges sociales – RPC/RRQ et AE/RQAP</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales – FICA, FUTA y SUTA</t>
+          <t>Cargas sociales – CPP/QPP y EI/QPIP</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Encargos – FICA, FUTA e SUTA</t>
+          <t>Encargos – CPP/QPP e EI/QPIP</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n">
-        <v>6160</v>
+        <v>6155</v>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>coa.6160.name</t>
+          <t>coa.6155.name</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Payroll burden – employer health tax and workers’ compensation</t>
+          <t>Payroll burden – FICA, FUTA and SUTA</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Charges sociales – impôt-santé et indemnisation des accidentés</t>
+          <t>Charges sociales – FICA, FUTA et SUTA</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Cargas sociales – impuesto de salud y riesgos laborales</t>
+          <t>Cargas sociales – FICA, FUTA y SUTA</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>Encargos – imposto de saúde e seguro de acidentes</t>
+          <t>Encargos – FICA, FUTA e SUTA</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
-        <v>6165</v>
+        <v>6160</v>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>coa.6165.name</t>
+          <t>coa.6160.name</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Benefits and retirement plan contributions</t>
+          <t>Payroll burden – employer health tax and workers’ compensation</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Avantages sociaux et cotisations aux régimes de retraite</t>
+          <t>Charges sociales – impôt-santé et indemnisation des accidentés</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Beneficios y aportes a planes de jubilación</t>
+          <t>Cargas sociales – impuesto de salud y riesgos laborales</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Benefícios e contribuições a planos de previdência</t>
+          <t>Encargos – imposto de saúde e seguro de acidentes</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n">
-        <v>6170</v>
+        <v>6165</v>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>coa.6170.name</t>
+          <t>coa.6165.name</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Vacation and statutory holiday pay – administration</t>
+          <t>Benefits and retirement plan contributions</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Vacances et jours fériés – administration</t>
+          <t>Avantages sociaux et cotisations aux régimes de retraite</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Vacaciones y feriados – administración</t>
+          <t>Beneficios y aportes a planes de jubilación</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>Férias e feriados – administração</t>
+          <t>Benefícios e contribuições a planos de previdência</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>coa.6200.name</t>
+          <t>coa.6170.name</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Insurance – general liability, property and vehicles</t>
+          <t>Vacation and statutory holiday pay – administration</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Assurances – responsabilité civile, biens et véhicules</t>
+          <t>Vacances et jours fériés – administration</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Seguros – responsabilidad general, bienes y vehículos</t>
+          <t>Vacaciones y feriados – administración</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Seguros – responsabilidade geral, bens e veículos</t>
+          <t>Férias e feriados – administração</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>coa.6300.name</t>
+          <t>coa.6200.name</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Rent – office, hangar and storage</t>
+          <t>Insurance – general liability, property and vehicles</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Loyer – bureau, hangar et entreposage</t>
+          <t>Assurances – responsabilité civile, biens et véhicules</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Alquiler – oficina, hangar y depósito</t>
+          <t>Seguros – responsabilidad general, bienes y vehículos</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>Aluguel – escritório, hangar e depósito</t>
+          <t>Seguros – responsabilidade geral, bens e veículos</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
-        <v>6310</v>
+        <v>6300</v>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>coa.6310.name</t>
+          <t>coa.6300.name</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent – office, hangar and storage</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Services publics</t>
+          <t>Loyer – bureau, hangar et entreposage</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Servicios públicos</t>
+          <t>Alquiler – oficina, hangar y depósito</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Utilidades (água, luz, gás)</t>
+          <t>Aluguel – escritório, hangar e depósito</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
-        <v>6320</v>
+        <v>6310</v>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>coa.6320.name</t>
+          <t>coa.6310.name</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Telephone, internet and satellite communications</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Téléphone, internet et communications par satellite</t>
+          <t>Services publics</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Teléfono, internet y comunicaciones satelitales</t>
+          <t>Servicios públicos</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>Telefone, internet e comunicações via satélite</t>
+          <t>Utilidades (água, luz, gás)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
-        <v>6330</v>
+        <v>6320</v>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>coa.6330.name</t>
+          <t>coa.6320.name</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Property taxes</t>
+          <t>Telephone, internet and satellite communications</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Impôts fonciers</t>
+          <t>Téléphone, internet et communications par satellite</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Impuestos a la propiedad</t>
+          <t>Teléfono, internet y comunicaciones satelitales</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Impostos sobre a propriedade</t>
+          <t>Telefone, internet e comunicações via satélite</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>coa.6340.name</t>
+          <t>coa.6330.name</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Repairs and maintenance – buildings and hangars</t>
+          <t>Property taxes</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Réparations et entretien – bâtiments et hangars</t>
+          <t>Impôts fonciers</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Reparaciones y mantenimiento – edificios y hangares</t>
+          <t>Impuestos a la propiedad</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>Reparos e manutenção – edificações e hangares</t>
+          <t>Impostos sobre a propriedade</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
-        <v>6350</v>
+        <v>6340</v>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>coa.6350.name</t>
+          <t>coa.6340.name</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Repairs and maintenance – airstrips, yards and containment</t>
+          <t>Repairs and maintenance – buildings and hangars</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Réparations et entretien – pistes, cours et confinement</t>
+          <t>Réparations et entretien – bâtiments et hangars</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Reparaciones y mantenimiento – pistas, patios y contención</t>
+          <t>Reparaciones y mantenimiento – edificios y hangares</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Reparos e manutenção – pistas, pátios e contenção</t>
+          <t>Reparos e manutenção – edificações e hangares</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
-        <v>6400</v>
+        <v>6350</v>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>coa.6400.name</t>
+          <t>coa.6350.name</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Repairs and maintenance – airstrips, yards and containment</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Honoraires juridiques</t>
+          <t>Réparations et entretien – pistes, cours et confinement</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Honorarios legales</t>
+          <t>Reparaciones y mantenimiento – pistas, patios y contención</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Honorários advocatícios</t>
+          <t>Reparos e manutenção – pistas, pátios e contenção</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
-        <v>6410</v>
+        <v>6400</v>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>coa.6410.name</t>
+          <t>coa.6400.name</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Accounting and audit fees</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Honoraires de comptabilité et de vérification</t>
+          <t>Honoraires juridiques</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Honorarios de contabilidad y auditoría</t>
+          <t>Honorarios legales</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Honorários contábeis e de auditoria</t>
+          <t>Honorários advocatícios</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n">
-        <v>6420</v>
+        <v>6410</v>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>coa.6420.name</t>
+          <t>coa.6410.name</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Consulting and professional fees</t>
+          <t>Accounting and audit fees</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Honoraires de consultation et professionnels</t>
+          <t>Honoraires de comptabilité et de vérification</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Honorarios de consultoría y profesionales</t>
+          <t>Honorarios de contabilidad y auditoría</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Honorários de consultoria e profissionais</t>
+          <t>Honorários contábeis e de auditoria</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
-        <v>6500</v>
+        <v>6420</v>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>coa.6500.name</t>
+          <t>coa.6420.name</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Aviation certificates and regulatory fees (TC / FAA)</t>
+          <t>Consulting and professional fees</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Certificats d’aviation et droits réglementaires (TC / FAA)</t>
+          <t>Honoraires de consultation et professionnels</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Certificados aeronáuticos y tasas regulatorias (TC / FAA)</t>
+          <t>Honorarios de consultoría y profesionales</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Certificados aeronáuticos e taxas regulatórias (TC / FAA)</t>
+          <t>Honorários de consultoria e profissionais</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n">
-        <v>6510</v>
+        <v>6500</v>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>coa.6510.name</t>
+          <t>coa.6500.name</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Pesticide applicator licences, permits and registrations</t>
+          <t>Aviation certificates and regulatory fees (TC / FAA)</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Permis et certificats d’applicateur de pesticides</t>
+          <t>Certificats d’aviation et droits réglementaires (TC / FAA)</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Licencias, permisos y registros de aplicador de plaguicidas</t>
+          <t>Certificados aeronáuticos y tasas regulatorias (TC / FAA)</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Licenças, autorizações e registros de aplicador de defensivos</t>
+          <t>Certificados aeronáuticos e taxas regulatórias (TC / FAA)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
-        <v>6520</v>
+        <v>6510</v>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>coa.6520.name</t>
+          <t>coa.6510.name</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Memberships and associations</t>
+          <t>Pesticide applicator licences, permits and registrations</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Cotisations et associations</t>
+          <t>Permis et certificats d’applicateur de pesticides</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Membresías y asociaciones</t>
+          <t>Licencias, permisos y registros de aplicador de plaguicidas</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Associações e anuidades</t>
+          <t>Licenças, autorizações e registros de aplicador de defensivos</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n">
-        <v>6530</v>
+        <v>6520</v>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>coa.6530.name</t>
+          <t>coa.6520.name</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Training and recurrent training</t>
+          <t>Memberships and associations</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Formation et formation périodique</t>
+          <t>Cotisations et associations</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Capacitación y entrenamiento recurrente</t>
+          <t>Membresías y asociaciones</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Treinamento e reciclagem</t>
+          <t>Associações e anuidades</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
-        <v>6540</v>
+        <v>6530</v>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>coa.6540.name</t>
+          <t>coa.6530.name</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Safety equipment, PPE and environmental compliance</t>
+          <t>Training and recurrent training</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Équipement de sécurité, EPI et conformité environnementale</t>
+          <t>Formation et formation périodique</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Equipo de seguridad, EPP y cumplimiento ambiental</t>
+          <t>Capacitación y entrenamiento recurrente</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Equipamentos de segurança, EPI e conformidade ambiental</t>
+          <t>Treinamento e reciclagem</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
-        <v>6600</v>
+        <v>6540</v>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>coa.6600.name</t>
+          <t>coa.6540.name</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Office supplies and postage</t>
+          <t>Safety equipment, PPE and environmental compliance</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Fournitures de bureau et frais postaux</t>
+          <t>Équipement de sécurité, EPI et conformité environnementale</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Útiles de oficina y correo</t>
+          <t>Equipo de seguridad, EPP y cumplimiento ambiental</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>Material de escritório e correio</t>
+          <t>Equipamentos de segurança, EPI e conformidade ambiental</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n">
-        <v>6610</v>
+        <v>6600</v>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>coa.6610.name</t>
+          <t>coa.6600.name</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Software and subscriptions</t>
+          <t>Office supplies and postage</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Logiciels et abonnements</t>
+          <t>Fournitures de bureau et frais postaux</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Software y suscripciones</t>
+          <t>Útiles de oficina y correo</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Software e assinaturas</t>
+          <t>Material de escritório e correio</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="n">
-        <v>6620</v>
+        <v>6610</v>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>coa.6620.name</t>
+          <t>coa.6610.name</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Bank service charges</t>
+          <t>Software and subscriptions</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Frais bancaires</t>
+          <t>Logiciels et abonnements</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Comisiones bancarias</t>
+          <t>Software y suscripciones</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Software e assinaturas</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
-        <v>6630</v>
+        <v>6620</v>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>coa.6630.name</t>
+          <t>coa.6620.name</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Merchant and credit card fees</t>
+          <t>Bank service charges</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Frais de traitement des cartes de crédit</t>
+          <t>Frais bancaires</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Comisiones por tarjetas de crédito</t>
+          <t>Comisiones bancarias</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Taxas de cartão de crédito</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
-        <v>6640</v>
+        <v>6630</v>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>coa.6640.name</t>
+          <t>coa.6630.name</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Merchant and credit card fees</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Créances irrécouvrables</t>
+          <t>Frais de traitement des cartes de crédit</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Cuentas incobrables</t>
+          <t>Comisiones por tarjetas de crédito</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Perdas com devedores</t>
+          <t>Taxas de cartão de crédito</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
-        <v>6700</v>
+        <v>6640</v>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>coa.6700.name</t>
+          <t>coa.6640.name</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Vehicle expenses – administration</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Frais de véhicules – administration</t>
+          <t>Créances irrécouvrables</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Gastos de vehículos – administración</t>
+          <t>Cuentas incobrables</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Despesas com veículos – administração</t>
+          <t>Perdas com devedores</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>coa.6800.name</t>
+          <t>coa.6700.name</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Travel – administration</t>
+          <t>Vehicle expenses – administration</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Déplacements – administration</t>
+          <t>Frais de véhicules – administration</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>Viajes – administración</t>
+          <t>Gastos de vehículos – administración</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>Viagens – administração</t>
+          <t>Despesas com veículos – administração</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
-        <v>6810</v>
+        <v>6800</v>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>coa.6810.name</t>
+          <t>coa.6800.name</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
+          <t>Travel – administration</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Repas et frais de représentation</t>
+          <t>Déplacements – administration</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Comidas y representación</t>
+          <t>Viajes – administración</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Refeições e representação</t>
+          <t>Viagens – administração</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="n">
-        <v>6900</v>
+        <v>6810</v>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>coa.6900.name</t>
+          <t>coa.6810.name</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Amortization – buildings, office and other assets</t>
+          <t>Meals and entertainment</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Amortissement – bâtiments, bureau et autres actifs</t>
+          <t>Repas et frais de représentation</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>Depreciación – edificios, oficina y otros activos</t>
+          <t>Comidas y representación</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>Depreciação – edificações, escritório e outros ativos</t>
+          <t>Refeições e representação</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
-        <v>6910</v>
+        <v>6900</v>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>coa.6910.name</t>
+          <t>coa.6900.name</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Amortization – intangible assets</t>
+          <t>Amortization – buildings, office and other assets</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Amortissement – actifs incorporels</t>
+          <t>Amortissement – bâtiments, bureau et autres actifs</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Amortización – activos intangibles</t>
+          <t>Depreciación – edificios, oficina y otros activos</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>Amortização – ativos intangíveis</t>
+          <t>Depreciação – edificações, escritório e outros ativos</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
-        <v>6950</v>
+        <v>6910</v>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>coa.6950.name</t>
+          <t>coa.6910.name</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Small tools and minor equipment</t>
+          <t>Amortization – intangible assets</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Petits outils et équipement mineur</t>
+          <t>Amortissement – actifs incorporels</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Herramientas menores y equipo menor</t>
+          <t>Amortización – activos intangibles</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>Ferramentas e equipamentos de pequeno valor</t>
+          <t>Amortização – ativos intangíveis</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
+        <v>6950</v>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>coa.6950.name</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Small tools and minor equipment</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>Petits outils et équipement mineur</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>Herramientas menores y equipo menor</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>Ferramentas e equipamentos de pequeno valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
         <v>6990</v>
       </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>coa.6990.name</t>
         </is>
       </c>
-      <c r="C219" s="4" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
         <is>
           <t>Miscellaneous expenses</t>
         </is>
       </c>
-      <c r="D219" s="4" t="inlineStr">
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>Charges diverses</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr">
+      <c r="E220" s="4" t="inlineStr">
         <is>
           <t>Gastos varios</t>
         </is>
       </c>
-      <c r="F219" s="4" t="inlineStr">
+      <c r="F220" s="4" t="inlineStr">
         <is>
           <t>Despesas diversas</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="11" t="n">
+    <row r="221">
+      <c r="A221" s="11" t="n">
         <v>7000</v>
       </c>
-      <c r="B220" s="11" t="inlineStr">
+      <c r="B221" s="11" t="inlineStr">
         <is>
           <t>coa.7000.name</t>
         </is>
       </c>
-      <c r="C220" s="11" t="inlineStr">
+      <c r="C221" s="11" t="inlineStr">
         <is>
           <t>Other income and expenses</t>
         </is>
       </c>
-      <c r="D220" s="11" t="inlineStr">
+      <c r="D221" s="11" t="inlineStr">
         <is>
           <t>Autres produits et charges</t>
         </is>
       </c>
-      <c r="E220" s="11" t="inlineStr">
+      <c r="E221" s="11" t="inlineStr">
         <is>
           <t>Otros ingresos y gastos</t>
         </is>
       </c>
-      <c r="F220" s="11" t="inlineStr">
+      <c r="F221" s="11" t="inlineStr">
         <is>
           <t>Outras receitas e despesas</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="n">
-        <v>7010</v>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>coa.7010.name</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr">
-        <is>
-          <t>Revenus d’intérêts</t>
-        </is>
-      </c>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>Ingresos por intereses</t>
-        </is>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>Receitas de juros</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="n">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>coa.7020.name</t>
+          <t>coa.7010.name</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Foreign exchange gains and losses</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Gains et pertes de change</t>
+          <t>Revenus d’intérêts</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>Ganancias y pérdidas cambiarias</t>
+          <t>Ingresos por intereses</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>Ganhos e perdas cambiais</t>
+          <t>Receitas de juros</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
-        <v>7030</v>
+        <v>7020</v>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>coa.7030.name</t>
+          <t>coa.7020.name</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Gain or loss on disposal of assets</t>
+          <t>Foreign exchange gains and losses</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Gain ou perte sur cession d’actifs</t>
+          <t>Gains et pertes de change</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Ganancia o pérdida por venta de activos</t>
+          <t>Ganancias y pérdidas cambiarias</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Ganho ou perda na alienação de ativos</t>
+          <t>Ganhos e perdas cambiais</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n">
-        <v>7040</v>
+        <v>7030</v>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>coa.7040.name</t>
+          <t>coa.7030.name</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Government grants and subsidies</t>
+          <t>Gain or loss on disposal of assets</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Subventions gouvernementales</t>
+          <t>Gain ou perte sur cession d’actifs</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Subvenciones gubernamentales</t>
+          <t>Ganancia o pérdida por venta de activos</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>Subvenções governamentais</t>
+          <t>Ganho ou perda na alienação de ativos</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>coa.7050.name</t>
+          <t>coa.7040.name</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Fuel tax credits and refunds</t>
+          <t>Government grants and subsidies</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Crédits et remboursements de taxe sur les carburants</t>
+          <t>Subventions gouvernementales</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>Créditos y reembolsos de impuestos al combustible</t>
+          <t>Subvenciones gubernamentales</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Créditos e restituições de impostos sobre combustível</t>
+          <t>Subvenções governamentais</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="n">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>coa.7060.name</t>
+          <t>coa.7050.name</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Insurance proceeds and recoveries</t>
+          <t>Fuel tax credits and refunds</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Produits d’assurance et recouvrements</t>
+          <t>Crédits et remboursements de taxe sur les carburants</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Indemnizaciones de seguros y recuperaciones</t>
+          <t>Créditos y reembolsos de impuestos al combustible</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>Indenizações de seguros e recuperações</t>
+          <t>Créditos e restituições de impostos sobre combustível</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
-        <v>7100</v>
+        <v>7060</v>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>coa.7100.name</t>
+          <t>coa.7060.name</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Interest – aircraft and equipment loans</t>
+          <t>Insurance proceeds and recoveries</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Intérêts – prêts sur aéronefs et équipement</t>
+          <t>Produits d’assurance et recouvrements</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Intereses – préstamos de aeronaves y equipos</t>
+          <t>Indemnizaciones de seguros y recuperaciones</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Juros – financiamentos de aeronaves e equipamentos</t>
+          <t>Indenizações de seguros e recuperações</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n">
-        <v>7110</v>
+        <v>7100</v>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>coa.7110.name</t>
+          <t>coa.7100.name</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Interest – operating line and other</t>
+          <t>Interest – aircraft and equipment loans</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Intérêts – marge de crédit et autres</t>
+          <t>Intérêts – prêts sur aéronefs et équipement</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Intereses – línea de crédito y otros</t>
+          <t>Intereses – préstamos de aeronaves y equipos</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>Juros – linha de crédito e outros</t>
+          <t>Juros – financiamentos de aeronaves e equipamentos</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>coa.7120.name</t>
+          <t>coa.7110.name</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Interest on lease liabilities</t>
+          <t>Interest – operating line and other</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Intérêts sur obligations locatives</t>
+          <t>Intérêts – marge de crédit et autres</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Intereses sobre pasivos por arrendamiento</t>
+          <t>Intereses – línea de crédito y otros</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Juros sobre passivos de arrendamento</t>
+          <t>Juros – linha de crédito e outros</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n">
+        <v>7120</v>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>coa.7120.name</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Interest on lease liabilities</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>Intérêts sur obligations locatives</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>Intereses sobre pasivos por arrendamiento</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>Juros sobre passivos de arrendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n">
         <v>7200</v>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B231" s="4" t="inlineStr">
         <is>
           <t>coa.7200.name</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr">
+      <c r="C231" s="4" t="inlineStr">
         <is>
           <t>Penalties, fines and non-deductible expenses</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D231" s="4" t="inlineStr">
         <is>
           <t>Pénalités, amendes et charges non déductibles</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
+      <c r="E231" s="4" t="inlineStr">
         <is>
           <t>Multas, sanciones y gastos no deducibles</t>
         </is>
       </c>
-      <c r="F230" s="4" t="inlineStr">
+      <c r="F231" s="4" t="inlineStr">
         <is>
           <t>Multas, penalidades e despesas não dedutíveis</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="11" t="n">
+    <row r="232">
+      <c r="A232" s="11" t="n">
         <v>8000</v>
       </c>
-      <c r="B231" s="11" t="inlineStr">
+      <c r="B232" s="11" t="inlineStr">
         <is>
           <t>coa.8000.name</t>
         </is>
       </c>
-      <c r="C231" s="11" t="inlineStr">
+      <c r="C232" s="11" t="inlineStr">
         <is>
           <t>Income taxes</t>
         </is>
       </c>
-      <c r="D231" s="11" t="inlineStr">
+      <c r="D232" s="11" t="inlineStr">
         <is>
           <t>Impôts sur le revenu</t>
         </is>
       </c>
-      <c r="E231" s="11" t="inlineStr">
+      <c r="E232" s="11" t="inlineStr">
         <is>
           <t>Impuestos sobre la renta</t>
         </is>
       </c>
-      <c r="F231" s="11" t="inlineStr">
+      <c r="F232" s="11" t="inlineStr">
         <is>
           <t>Imposto de renda</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="4" t="n">
-        <v>8010</v>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>coa.8010.name</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>Current income taxes</t>
-        </is>
-      </c>
-      <c r="D232" s="4" t="inlineStr">
-        <is>
-          <t>Impôts sur le revenu exigibles</t>
-        </is>
-      </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>Impuesto sobre la renta corriente</t>
-        </is>
-      </c>
-      <c r="F232" s="4" t="inlineStr">
-        <is>
-          <t>Imposto de renda corrente</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
+        <v>8010</v>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>coa.8010.name</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>Current income taxes</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>Impôts sur le revenu exigibles</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>Impuesto sobre la renta corriente</t>
+        </is>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>Imposto de renda corrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n">
         <v>8020</v>
       </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr">
         <is>
           <t>coa.8020.name</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr">
+      <c r="C234" s="4" t="inlineStr">
         <is>
           <t>Deferred income taxes</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D234" s="4" t="inlineStr">
         <is>
           <t>Impôts sur le revenu différés</t>
         </is>
       </c>
-      <c r="E233" s="4" t="inlineStr">
+      <c r="E234" s="4" t="inlineStr">
         <is>
           <t>Impuesto sobre la renta diferido</t>
         </is>
       </c>
-      <c r="F233" s="4" t="inlineStr">
+      <c r="F234" s="4" t="inlineStr">
         <is>
           <t>Imposto de renda diferido</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="12" t="inlineStr">
+    <row r="235"/>
+    <row r="236">
+      <c r="A236" s="12" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" s="13" t="inlineStr">
+      <c r="C236" s="13" t="inlineStr">
         <is>
           <t>Translations are drafts for review by a native-speaking accountant. fr-CA follows Canadian (CPA Canada / CRA) terminology: TPS/TVH, RPC/RRQ, AE/RQAP. Tax program names (GST/HST, FICA, CPP) are kept in English where there is no local equivalent.</t>
         </is>
@@ -24655,7 +24750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D215"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27307,52 +27402,52 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="13" t="n">
-        <v>4900</v>
-      </c>
-      <c r="B133" s="13" t="inlineStr">
-        <is>
-          <t>Sales discounts, rebates and allowances</t>
-        </is>
-      </c>
-      <c r="C133" s="13" t="inlineStr">
+      <c r="A133" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Miscellaneous and other income</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="D133" s="13" t="inlineStr">
-        <is>
-          <t>Discounts/Refunds Given</t>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Other Primary Income</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="13" t="n">
-        <v>5010</v>
+        <v>4900</v>
       </c>
       <c r="B134" s="13" t="inlineStr">
         <is>
-          <t>Chemical cost of sales (company-owned)</t>
+          <t>Sales discounts, rebates and allowances</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>Cost of Goods Sold</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials - COGS</t>
+          <t>Discounts/Refunds Given</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="13" t="n">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>Fertilizer and seed cost of sales</t>
+          <t>Chemical cost of sales (company-owned)</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
@@ -27368,11 +27463,11 @@
     </row>
     <row r="136">
       <c r="A136" s="13" t="n">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>Supplier rebates and early-order discounts</t>
+          <t>Fertilizer and seed cost of sales</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
@@ -27388,11 +27483,11 @@
     </row>
     <row r="137">
       <c r="A137" s="13" t="n">
-        <v>5100</v>
+        <v>5030</v>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>Aviation fuel and oil</t>
+          <t>Supplier rebates and early-order discounts</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
@@ -27408,11 +27503,11 @@
     </row>
     <row r="138">
       <c r="A138" s="13" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>Pilot wages</t>
+          <t>Aviation fuel and oil</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
@@ -27422,17 +27517,17 @@
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>Cost of labor - COS</t>
+          <t>Supplies &amp; Materials - COGS</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="13" t="n">
-        <v>5210</v>
+        <v>5200</v>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>Loader and ground crew wages</t>
+          <t>Pilot wages</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
@@ -27448,11 +27543,11 @@
     </row>
     <row r="140">
       <c r="A140" s="13" t="n">
-        <v>5220</v>
+        <v>5210</v>
       </c>
       <c r="B140" s="13" t="inlineStr">
         <is>
-          <t>Maintenance labour – AMEs and mechanics</t>
+          <t>Loader and ground crew wages</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
@@ -27468,11 +27563,11 @@
     </row>
     <row r="141">
       <c r="A141" s="13" t="n">
-        <v>5250</v>
+        <v>5220</v>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>Direct payroll burden – CPP/QPP and EI/QPIP</t>
+          <t>Maintenance labour – AMEs and mechanics</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
@@ -27488,11 +27583,11 @@
     </row>
     <row r="142">
       <c r="A142" s="13" t="n">
-        <v>5255</v>
+        <v>5250</v>
       </c>
       <c r="B142" s="13" t="inlineStr">
         <is>
-          <t>Direct payroll burden – FICA, FUTA and SUTA</t>
+          <t>Direct payroll burden – CPP/QPP and EI/QPIP</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
@@ -27508,11 +27603,11 @@
     </row>
     <row r="143">
       <c r="A143" s="13" t="n">
-        <v>5260</v>
+        <v>5255</v>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>Direct payroll burden – employer health tax and workers’ compensation</t>
+          <t>Direct payroll burden – FICA, FUTA and SUTA</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
@@ -27528,11 +27623,11 @@
     </row>
     <row r="144">
       <c r="A144" s="13" t="n">
-        <v>5265</v>
+        <v>5260</v>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>Direct payroll burden – benefits and retirement contributions</t>
+          <t>Direct payroll burden – employer health tax and workers’ compensation</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
@@ -27548,11 +27643,11 @@
     </row>
     <row r="145">
       <c r="A145" s="13" t="n">
-        <v>5270</v>
+        <v>5265</v>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>Direct payroll – vacation and statutory holiday pay</t>
+          <t>Direct payroll burden – benefits and retirement contributions</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
@@ -27568,11 +27663,11 @@
     </row>
     <row r="146">
       <c r="A146" s="13" t="n">
-        <v>5300</v>
+        <v>5270</v>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – parts issued</t>
+          <t>Direct payroll – vacation and statutory holiday pay</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
@@ -27582,17 +27677,17 @@
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>Other Costs of Services - COS</t>
+          <t>Cost of labor - COS</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="13" t="n">
-        <v>5310</v>
+        <v>5300</v>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – outside services</t>
+          <t>Aircraft maintenance – parts issued</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
@@ -27608,11 +27703,11 @@
     </row>
     <row r="148">
       <c r="A148" s="13" t="n">
-        <v>5320</v>
+        <v>5310</v>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – engine and propeller overhauls (expensed)</t>
+          <t>Aircraft maintenance – outside services</t>
         </is>
       </c>
       <c r="C148" s="13" t="inlineStr">
@@ -27628,11 +27723,11 @@
     </row>
     <row r="149">
       <c r="A149" s="13" t="n">
-        <v>5330</v>
+        <v>5320</v>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – components, avionics and dispersal systems</t>
+          <t>Aircraft maintenance – engine and propeller overhauls (expensed)</t>
         </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
@@ -27648,11 +27743,11 @@
     </row>
     <row r="150">
       <c r="A150" s="13" t="n">
-        <v>5340</v>
+        <v>5330</v>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>Aircraft maintenance – shop consumables</t>
+          <t>Aircraft maintenance – components, avionics and dispersal systems</t>
         </is>
       </c>
       <c r="C150" s="13" t="inlineStr">
@@ -27668,11 +27763,11 @@
     </row>
     <row r="151">
       <c r="A151" s="13" t="n">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>Aircraft hull insurance</t>
+          <t>Aircraft maintenance – shop consumables</t>
         </is>
       </c>
       <c r="C151" s="13" t="inlineStr">
@@ -27688,11 +27783,11 @@
     </row>
     <row r="152">
       <c r="A152" s="13" t="n">
-        <v>5410</v>
+        <v>5400</v>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>Aviation and aerial application liability insurance</t>
+          <t>Aircraft hull insurance</t>
         </is>
       </c>
       <c r="C152" s="13" t="inlineStr">
@@ -27708,11 +27803,11 @@
     </row>
     <row r="153">
       <c r="A153" s="13" t="n">
-        <v>5500</v>
+        <v>5410</v>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Aircraft leases and rentals</t>
+          <t>Aviation and aerial application liability insurance</t>
         </is>
       </c>
       <c r="C153" s="13" t="inlineStr">
@@ -27722,17 +27817,17 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>Equipment Rental - COS</t>
+          <t>Other Costs of Services - COS</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="13" t="n">
-        <v>5510</v>
+        <v>5500</v>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>Hangar, tie-down and landing fees</t>
+          <t>Aircraft leases and rentals</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
@@ -27742,17 +27837,17 @@
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>Other Costs of Services - COS</t>
+          <t>Equipment Rental - COS</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="13" t="n">
-        <v>5600</v>
+        <v>5510</v>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>GPS, guidance and flight-tracking subscriptions</t>
+          <t>Hangar, tie-down and landing fees</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
@@ -27768,11 +27863,11 @@
     </row>
     <row r="156">
       <c r="A156" s="13" t="n">
-        <v>5610</v>
+        <v>5600</v>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>Crew travel, lodging and per diem</t>
+          <t>GPS, guidance and flight-tracking subscriptions</t>
         </is>
       </c>
       <c r="C156" s="13" t="inlineStr">
@@ -27788,11 +27883,11 @@
     </row>
     <row r="157">
       <c r="A157" s="13" t="n">
-        <v>5620</v>
+        <v>5610</v>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>Ground support vehicle fuel</t>
+          <t>Crew travel, lodging and per diem</t>
         </is>
       </c>
       <c r="C157" s="13" t="inlineStr">
@@ -27808,11 +27903,11 @@
     </row>
     <row r="158">
       <c r="A158" s="13" t="n">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="B158" s="13" t="inlineStr">
         <is>
-          <t>Vehicle and equipment maintenance – parts issued</t>
+          <t>Ground support vehicle fuel</t>
         </is>
       </c>
       <c r="C158" s="13" t="inlineStr">
@@ -27828,11 +27923,11 @@
     </row>
     <row r="159">
       <c r="A159" s="13" t="n">
-        <v>5640</v>
+        <v>5630</v>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>Vehicle and equipment maintenance – outside services</t>
+          <t>Vehicle and equipment maintenance – parts issued</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
@@ -27848,11 +27943,11 @@
     </row>
     <row r="160">
       <c r="A160" s="13" t="n">
-        <v>5650</v>
+        <v>5640</v>
       </c>
       <c r="B160" s="13" t="inlineStr">
         <is>
-          <t>Equipment and vehicle rentals</t>
+          <t>Vehicle and equipment maintenance – outside services</t>
         </is>
       </c>
       <c r="C160" s="13" t="inlineStr">
@@ -27862,17 +27957,17 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>Equipment Rental - COS</t>
+          <t>Other Costs of Services - COS</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="13" t="n">
-        <v>5700</v>
+        <v>5650</v>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>Subcontracted aerial application</t>
+          <t>Equipment and vehicle rentals</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
@@ -27882,17 +27977,17 @@
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>Other Costs of Services - COS</t>
+          <t>Equipment Rental - COS</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="13" t="n">
-        <v>5710</v>
+        <v>5700</v>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>Containment, rinsate and disposal costs</t>
+          <t>Subcontracted aerial application</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
@@ -27908,11 +28003,11 @@
     </row>
     <row r="163">
       <c r="A163" s="13" t="n">
-        <v>5800</v>
+        <v>5710</v>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>Amortization – aircraft</t>
+          <t>Containment, rinsate and disposal costs</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
@@ -27928,11 +28023,11 @@
     </row>
     <row r="164">
       <c r="A164" s="13" t="n">
-        <v>5810</v>
+        <v>5800</v>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>Amortization – vehicles and ground equipment</t>
+          <t>Amortization – aircraft</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
@@ -27948,11 +28043,11 @@
     </row>
     <row r="165">
       <c r="A165" s="13" t="n">
-        <v>5900</v>
+        <v>5810</v>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>Inventory adjustments – parts</t>
+          <t>Amortization – vehicles and ground equipment</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
@@ -27962,17 +28057,17 @@
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials - COGS</t>
+          <t>Other Costs of Services - COS</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="13" t="n">
-        <v>5910</v>
+        <v>5900</v>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>Inventory adjustments – chemicals and fuel</t>
+          <t>Inventory adjustments – parts</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
@@ -27988,11 +28083,11 @@
     </row>
     <row r="167">
       <c r="A167" s="13" t="n">
-        <v>5920</v>
+        <v>5910</v>
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>Freight-in, customs and duty</t>
+          <t>Inventory adjustments – chemicals and fuel</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
@@ -28008,31 +28103,31 @@
     </row>
     <row r="168">
       <c r="A168" s="13" t="n">
-        <v>6010</v>
+        <v>5920</v>
       </c>
       <c r="B168" s="13" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
+          <t>Freight-in, customs and duty</t>
         </is>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cost of Goods Sold</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>Advertising/Promotional</t>
+          <t>Supplies &amp; Materials - COGS</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="13" t="n">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>Trade shows and association events</t>
+          <t>Advertising and promotion</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
@@ -28048,11 +28143,11 @@
     </row>
     <row r="170">
       <c r="A170" s="13" t="n">
-        <v>6100</v>
+        <v>6020</v>
       </c>
       <c r="B170" s="13" t="inlineStr">
         <is>
-          <t>Salaries – management</t>
+          <t>Trade shows and association events</t>
         </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
@@ -28062,17 +28157,17 @@
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>Officers' Compensation</t>
+          <t>Advertising/Promotional</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="13" t="n">
-        <v>6110</v>
+        <v>6100</v>
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>Salaries – office and dispatch staff</t>
+          <t>Salaries – management</t>
         </is>
       </c>
       <c r="C171" s="13" t="inlineStr">
@@ -28082,17 +28177,17 @@
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>Payroll Expenses</t>
+          <t>Officers' Compensation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="13" t="n">
-        <v>6150</v>
+        <v>6110</v>
       </c>
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>Payroll burden – CPP/QPP and EI/QPIP</t>
+          <t>Salaries – office and dispatch staff</t>
         </is>
       </c>
       <c r="C172" s="13" t="inlineStr">
@@ -28108,11 +28203,11 @@
     </row>
     <row r="173">
       <c r="A173" s="13" t="n">
-        <v>6155</v>
+        <v>6150</v>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>Payroll burden – FICA, FUTA and SUTA</t>
+          <t>Payroll burden – CPP/QPP and EI/QPIP</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
@@ -28128,11 +28223,11 @@
     </row>
     <row r="174">
       <c r="A174" s="13" t="n">
-        <v>6160</v>
+        <v>6155</v>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>Payroll burden – employer health tax and workers’ compensation</t>
+          <t>Payroll burden – FICA, FUTA and SUTA</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
@@ -28148,11 +28243,11 @@
     </row>
     <row r="175">
       <c r="A175" s="13" t="n">
-        <v>6165</v>
+        <v>6160</v>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>Benefits and retirement plan contributions</t>
+          <t>Payroll burden – employer health tax and workers’ compensation</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
@@ -28168,11 +28263,11 @@
     </row>
     <row r="176">
       <c r="A176" s="13" t="n">
-        <v>6170</v>
+        <v>6165</v>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>Vacation and statutory holiday pay – administration</t>
+          <t>Benefits and retirement plan contributions</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
@@ -28188,11 +28283,11 @@
     </row>
     <row r="177">
       <c r="A177" s="13" t="n">
-        <v>6200</v>
+        <v>6170</v>
       </c>
       <c r="B177" s="13" t="inlineStr">
         <is>
-          <t>Insurance – general liability, property and vehicles</t>
+          <t>Vacation and statutory holiday pay – administration</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
@@ -28202,17 +28297,17 @@
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payroll Expenses</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="13" t="n">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>Rent – office, hangar and storage</t>
+          <t>Insurance – general liability, property and vehicles</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
@@ -28222,17 +28317,17 @@
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>Rent or Lease of Buildings</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="13" t="n">
-        <v>6310</v>
+        <v>6300</v>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent – office, hangar and storage</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
@@ -28242,17 +28337,17 @@
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Rent or Lease of Buildings</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="13" t="n">
-        <v>6320</v>
+        <v>6310</v>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>Telephone, internet and satellite communications</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
@@ -28268,11 +28363,11 @@
     </row>
     <row r="181">
       <c r="A181" s="13" t="n">
-        <v>6330</v>
+        <v>6320</v>
       </c>
       <c r="B181" s="13" t="inlineStr">
         <is>
-          <t>Property taxes</t>
+          <t>Telephone, internet and satellite communications</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
@@ -28282,17 +28377,17 @@
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>Taxes Paid</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="13" t="n">
-        <v>6340</v>
+        <v>6330</v>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>Repairs and maintenance – buildings and hangars</t>
+          <t>Property taxes</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
@@ -28302,17 +28397,17 @@
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>Repair &amp; Maintenance</t>
+          <t>Taxes Paid</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="13" t="n">
-        <v>6350</v>
+        <v>6340</v>
       </c>
       <c r="B183" s="13" t="inlineStr">
         <is>
-          <t>Repairs and maintenance – airstrips, yards and containment</t>
+          <t>Repairs and maintenance – buildings and hangars</t>
         </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
@@ -28328,11 +28423,11 @@
     </row>
     <row r="184">
       <c r="A184" s="13" t="n">
-        <v>6400</v>
+        <v>6350</v>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Repairs and maintenance – airstrips, yards and containment</t>
         </is>
       </c>
       <c r="C184" s="13" t="inlineStr">
@@ -28342,17 +28437,17 @@
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>Legal &amp; Professional Fees</t>
+          <t>Repair &amp; Maintenance</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="13" t="n">
-        <v>6410</v>
+        <v>6400</v>
       </c>
       <c r="B185" s="13" t="inlineStr">
         <is>
-          <t>Accounting and audit fees</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="C185" s="13" t="inlineStr">
@@ -28368,11 +28463,11 @@
     </row>
     <row r="186">
       <c r="A186" s="13" t="n">
-        <v>6420</v>
+        <v>6410</v>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>Consulting and professional fees</t>
+          <t>Accounting and audit fees</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
@@ -28388,11 +28483,11 @@
     </row>
     <row r="187">
       <c r="A187" s="13" t="n">
-        <v>6500</v>
+        <v>6420</v>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>Aviation certificates and regulatory fees (TC / FAA)</t>
+          <t>Consulting and professional fees</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
@@ -28402,17 +28497,17 @@
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>Taxes Paid</t>
+          <t>Legal &amp; Professional Fees</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="13" t="n">
-        <v>6510</v>
+        <v>6500</v>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>Pesticide applicator licences, permits and registrations</t>
+          <t>Aviation certificates and regulatory fees (TC / FAA)</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
@@ -28428,11 +28523,11 @@
     </row>
     <row r="189">
       <c r="A189" s="13" t="n">
-        <v>6520</v>
+        <v>6510</v>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>Memberships and associations</t>
+          <t>Pesticide applicator licences, permits and registrations</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
@@ -28442,17 +28537,17 @@
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>Dues &amp; Subscriptions</t>
+          <t>Taxes Paid</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="13" t="n">
-        <v>6530</v>
+        <v>6520</v>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>Training and recurrent training</t>
+          <t>Memberships and associations</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
@@ -28462,17 +28557,17 @@
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Service Cost</t>
+          <t>Dues &amp; Subscriptions</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="13" t="n">
-        <v>6540</v>
+        <v>6530</v>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>Safety equipment, PPE and environmental compliance</t>
+          <t>Training and recurrent training</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
@@ -28482,17 +28577,17 @@
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials</t>
+          <t>Other Miscellaneous Service Cost</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="13" t="n">
-        <v>6600</v>
+        <v>6540</v>
       </c>
       <c r="B192" s="13" t="inlineStr">
         <is>
-          <t>Office supplies and postage</t>
+          <t>Safety equipment, PPE and environmental compliance</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
@@ -28502,17 +28597,17 @@
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>Office/General Administrative Expenses</t>
+          <t>Supplies &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="13" t="n">
-        <v>6610</v>
+        <v>6600</v>
       </c>
       <c r="B193" s="13" t="inlineStr">
         <is>
-          <t>Software and subscriptions</t>
+          <t>Office supplies and postage</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
@@ -28522,17 +28617,17 @@
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>Dues &amp; Subscriptions</t>
+          <t>Office/General Administrative Expenses</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="13" t="n">
-        <v>6620</v>
+        <v>6610</v>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>Bank service charges</t>
+          <t>Software and subscriptions</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
@@ -28542,17 +28637,17 @@
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Dues &amp; Subscriptions</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="13" t="n">
-        <v>6630</v>
+        <v>6620</v>
       </c>
       <c r="B195" s="13" t="inlineStr">
         <is>
-          <t>Merchant and credit card fees</t>
+          <t>Bank service charges</t>
         </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
@@ -28568,11 +28663,11 @@
     </row>
     <row r="196">
       <c r="A196" s="13" t="n">
-        <v>6640</v>
+        <v>6630</v>
       </c>
       <c r="B196" s="13" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Merchant and credit card fees</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
@@ -28582,17 +28677,17 @@
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>Bad Debts</t>
+          <t>Bank Charges</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="13" t="n">
-        <v>6700</v>
+        <v>6640</v>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>Vehicle expenses – administration</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
@@ -28602,17 +28697,17 @@
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Bad Debts</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="13" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="B198" s="13" t="inlineStr">
         <is>
-          <t>Travel – administration</t>
+          <t>Vehicle expenses – administration</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
@@ -28622,17 +28717,17 @@
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="13" t="n">
-        <v>6810</v>
+        <v>6800</v>
       </c>
       <c r="B199" s="13" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
+          <t>Travel – administration</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
@@ -28642,17 +28737,17 @@
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>Entertainment Meals</t>
+          <t>Travel</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="13" t="n">
-        <v>6900</v>
+        <v>6810</v>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>Amortization – buildings, office and other assets</t>
+          <t>Meals and entertainment</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
@@ -28662,17 +28757,17 @@
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Entertainment Meals</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="13" t="n">
-        <v>6910</v>
+        <v>6900</v>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>Amortization – intangible assets</t>
+          <t>Amortization – buildings, office and other assets</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
@@ -28682,17 +28777,17 @@
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Depreciation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="13" t="n">
-        <v>6950</v>
+        <v>6910</v>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>Small tools and minor equipment</t>
+          <t>Amortization – intangible assets</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
@@ -28702,17 +28797,17 @@
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>Supplies &amp; Materials</t>
+          <t>Amortization</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="13" t="n">
-        <v>6990</v>
+        <v>6950</v>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>Miscellaneous expenses</t>
+          <t>Small tools and minor equipment</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
@@ -28722,37 +28817,37 @@
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Service Cost</t>
+          <t>Supplies &amp; Materials</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="13" t="n">
-        <v>7010</v>
+        <v>6990</v>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Miscellaneous expenses</t>
         </is>
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>Interest Earned</t>
+          <t>Other Miscellaneous Service Cost</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="13" t="n">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>Foreign exchange gains and losses</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="C205" s="13" t="inlineStr">
@@ -28762,17 +28857,17 @@
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Income</t>
+          <t>Interest Earned</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="13" t="n">
-        <v>7030</v>
+        <v>7020</v>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>Gain or loss on disposal of assets</t>
+          <t>Foreign exchange gains and losses</t>
         </is>
       </c>
       <c r="C206" s="13" t="inlineStr">
@@ -28782,17 +28877,17 @@
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>Gain/Loss on Sale of Fixed Assets</t>
+          <t>Other Miscellaneous Income</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="13" t="n">
-        <v>7040</v>
+        <v>7030</v>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>Government grants and subsidies</t>
+          <t>Gain or loss on disposal of assets</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
@@ -28802,17 +28897,17 @@
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Income</t>
+          <t>Gain/Loss on Sale of Fixed Assets</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="13" t="n">
-        <v>7050</v>
+        <v>7040</v>
       </c>
       <c r="B208" s="13" t="inlineStr">
         <is>
-          <t>Fuel tax credits and refunds</t>
+          <t>Government grants and subsidies</t>
         </is>
       </c>
       <c r="C208" s="13" t="inlineStr">
@@ -28828,11 +28923,11 @@
     </row>
     <row r="209">
       <c r="A209" s="13" t="n">
-        <v>7060</v>
+        <v>7050</v>
       </c>
       <c r="B209" s="13" t="inlineStr">
         <is>
-          <t>Insurance proceeds and recoveries</t>
+          <t>Fuel tax credits and refunds</t>
         </is>
       </c>
       <c r="C209" s="13" t="inlineStr">
@@ -28848,31 +28943,31 @@
     </row>
     <row r="210">
       <c r="A210" s="13" t="n">
-        <v>7100</v>
+        <v>7060</v>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>Interest – aircraft and equipment loans</t>
+          <t>Insurance proceeds and recoveries</t>
         </is>
       </c>
       <c r="C210" s="13" t="inlineStr">
         <is>
-          <t>Other Expense</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Expense</t>
+          <t>Other Miscellaneous Income</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="13" t="n">
-        <v>7110</v>
+        <v>7100</v>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>Interest – operating line and other</t>
+          <t>Interest – aircraft and equipment loans</t>
         </is>
       </c>
       <c r="C211" s="13" t="inlineStr">
@@ -28888,11 +28983,11 @@
     </row>
     <row r="212">
       <c r="A212" s="13" t="n">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>Interest on lease liabilities</t>
+          <t>Interest – operating line and other</t>
         </is>
       </c>
       <c r="C212" s="13" t="inlineStr">
@@ -28908,11 +29003,11 @@
     </row>
     <row r="213">
       <c r="A213" s="13" t="n">
-        <v>7200</v>
+        <v>7120</v>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t>Penalties, fines and non-deductible expenses</t>
+          <t>Interest on lease liabilities</t>
         </is>
       </c>
       <c r="C213" s="13" t="inlineStr">
@@ -28922,17 +29017,17 @@
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>Penalties &amp; Settlements</t>
+          <t>Other Miscellaneous Expense</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="13" t="n">
-        <v>8010</v>
+        <v>7200</v>
       </c>
       <c r="B214" s="13" t="inlineStr">
         <is>
-          <t>Current income taxes</t>
+          <t>Penalties, fines and non-deductible expenses</t>
         </is>
       </c>
       <c r="C214" s="13" t="inlineStr">
@@ -28942,25 +29037,45 @@
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>Other Miscellaneous Expense</t>
+          <t>Penalties &amp; Settlements</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="13" t="n">
+        <v>8010</v>
+      </c>
+      <c r="B215" s="13" t="inlineStr">
+        <is>
+          <t>Current income taxes</t>
+        </is>
+      </c>
+      <c r="C215" s="13" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="D215" s="13" t="inlineStr">
+        <is>
+          <t>Other Miscellaneous Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="13" t="n">
         <v>8020</v>
       </c>
-      <c r="B215" s="13" t="inlineStr">
+      <c r="B216" s="13" t="inlineStr">
         <is>
           <t>Deferred income taxes</t>
         </is>
       </c>
-      <c r="C215" s="13" t="inlineStr">
+      <c r="C216" s="13" t="inlineStr">
         <is>
           <t>Other Expense</t>
         </is>
       </c>
-      <c r="D215" s="13" t="inlineStr">
+      <c r="D216" s="13" t="inlineStr">
         <is>
           <t>Other Miscellaneous Expense</t>
         </is>
